--- a/reports/Swiggy_Consolidated_Report.xlsx
+++ b/reports/Swiggy_Consolidated_Report.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,22 +200,17 @@
     <xf numFmtId="4" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -968,7 +963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1033,2212 +1028,2415 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="n">
+      <c r="A5" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="E5" s="30" t="n">
+      <c r="E5" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="F5" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="40" t="inlineStr">
+      <c r="F5" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="n">
+      <c r="A6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="38" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="32" t="n">
         <v>11007.2</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="32" t="n">
         <v>11007.2</v>
       </c>
-      <c r="F6" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="40" t="inlineStr">
+      <c r="F6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="30" t="n">
+      <c r="A7" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
-      <c r="C7" s="30" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="32" t="n">
         <v>524.2</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="32" t="n">
         <v>524.2</v>
       </c>
-      <c r="F7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="40" t="inlineStr">
+      <c r="F7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="30" t="n">
+      <c r="A8" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="39" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
-      <c r="C8" s="30" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="32" t="n">
         <v>7015.67</v>
       </c>
-      <c r="E8" s="33" t="n">
+      <c r="E8" s="32" t="n">
         <v>7015.67</v>
       </c>
-      <c r="F8" s="33" t="n">
+      <c r="F8" s="32" t="n">
         <v>-0</v>
       </c>
-      <c r="G8" s="40" t="inlineStr">
+      <c r="G8" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="30" t="n">
+      <c r="A9" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
-      <c r="C9" s="30" t="inlineStr">
+      <c r="C9" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="32" t="n">
         <v>6845.46</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="32" t="n">
         <v>6845.44</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="32" t="n">
         <v>-0.02</v>
       </c>
-      <c r="G9" s="40" t="inlineStr">
+      <c r="G9" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="30" t="n">
+      <c r="A10" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="39" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
-      <c r="C10" s="30" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="32" t="n">
         <v>6845.46</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="32" t="n">
         <v>6845.46</v>
       </c>
-      <c r="F10" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="40" t="inlineStr">
+      <c r="F10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="30" t="n">
+      <c r="A11" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="38" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C11" s="30" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="32" t="n">
         <v>6845.46</v>
       </c>
-      <c r="E11" s="33" t="n">
+      <c r="E11" s="32" t="n">
         <v>6845.46</v>
       </c>
-      <c r="F11" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="40" t="inlineStr">
+      <c r="F11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="30" t="n">
+      <c r="A12" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="39" t="inlineStr">
+      <c r="B12" s="38" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C12" s="30" t="inlineStr">
+      <c r="C12" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D12" s="30" t="n">
+      <c r="D12" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="E12" s="30" t="n">
+      <c r="E12" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="F12" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="40" t="inlineStr">
+      <c r="F12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="30" t="n">
+      <c r="A13" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
-      <c r="C13" s="30" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D13" s="33" t="n">
+      <c r="D13" s="32" t="n">
         <v>524.15</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="32" t="n">
         <v>524.2</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="32" t="n">
         <v>0.05</v>
       </c>
-      <c r="G13" s="40" t="inlineStr">
+      <c r="G13" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="n">
+      <c r="A14" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="38" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
-      <c r="C14" s="30" t="inlineStr">
+      <c r="C14" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D14" s="33" t="n">
+      <c r="D14" s="32" t="n">
         <v>10.48</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="32" t="n">
         <v>10.37</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="32" t="n">
         <v>-0.11</v>
       </c>
-      <c r="G14" s="40" t="inlineStr">
+      <c r="G14" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="n">
+      <c r="A15" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
-      <c r="C15" s="30" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="32" t="n">
         <v>518.25</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="32" t="n">
         <v>518.25</v>
       </c>
-      <c r="F15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="40" t="inlineStr">
+      <c r="F15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="n">
+      <c r="A16" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="38" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
-      <c r="C16" s="30" t="inlineStr">
+      <c r="C16" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="33" t="n">
+      <c r="D16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="32" t="n">
         <v>5.95</v>
       </c>
-      <c r="F16" s="33" t="n">
+      <c r="F16" s="32" t="n">
         <v>5.95</v>
       </c>
-      <c r="G16" s="41" t="inlineStr">
+      <c r="G16" s="40" t="inlineStr">
         <is>
           <t>EXPLAINED</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="30" t="n">
+      <c r="A17" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="D17" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="40" t="inlineStr">
+      <c r="D17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="n">
+      <c r="A18" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="39" t="inlineStr">
+      <c r="B18" s="38" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D18" s="30" t="n">
+      <c r="D18" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="E18" s="30" t="n">
+      <c r="E18" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="F18" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="40" t="inlineStr">
+      <c r="F18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="n">
+      <c r="A19" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
-      <c r="C19" s="30" t="inlineStr">
+      <c r="C19" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="32" t="n">
         <v>12017.28</v>
       </c>
-      <c r="E19" s="33" t="n">
+      <c r="E19" s="32" t="n">
         <v>12017.28</v>
       </c>
-      <c r="F19" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="40" t="inlineStr">
+      <c r="F19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="30" t="n">
+      <c r="A20" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="39" t="inlineStr">
+      <c r="B20" s="38" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
-      <c r="C20" s="30" t="inlineStr">
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="32" t="n">
         <v>572.28</v>
       </c>
-      <c r="E20" s="33" t="n">
+      <c r="E20" s="32" t="n">
         <v>572.28</v>
       </c>
-      <c r="F20" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="40" t="inlineStr">
+      <c r="F20" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="n">
+      <c r="A21" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B21" s="38" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
-      <c r="C21" s="30" t="inlineStr">
+      <c r="C21" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D21" s="33" t="n">
+      <c r="D21" s="32" t="n">
         <v>7649.3</v>
       </c>
-      <c r="E21" s="33" t="n">
+      <c r="E21" s="32" t="n">
         <v>7649.3</v>
       </c>
-      <c r="F21" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="40" t="inlineStr">
+      <c r="F21" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="30" t="n">
+      <c r="A22" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B22" s="38" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
-      <c r="C22" s="30" t="inlineStr">
+      <c r="C22" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D22" s="33" t="n">
+      <c r="D22" s="32" t="n">
         <v>7479.09</v>
       </c>
-      <c r="E22" s="33" t="n">
+      <c r="E22" s="32" t="n">
         <v>7479.13</v>
       </c>
-      <c r="F22" s="33" t="n">
+      <c r="F22" s="32" t="n">
         <v>0.04</v>
       </c>
-      <c r="G22" s="40" t="inlineStr">
+      <c r="G22" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="n">
+      <c r="A23" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="39" t="inlineStr">
+      <c r="B23" s="38" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
-      <c r="C23" s="30" t="inlineStr">
+      <c r="C23" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D23" s="33" t="n">
+      <c r="D23" s="32" t="n">
         <v>7479.09</v>
       </c>
-      <c r="E23" s="33" t="n">
+      <c r="E23" s="32" t="n">
         <v>7479.09</v>
       </c>
-      <c r="F23" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="40" t="inlineStr">
+      <c r="F23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="30" t="n">
+      <c r="A24" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B24" s="38" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C24" s="30" t="inlineStr">
+      <c r="C24" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D24" s="33" t="n">
+      <c r="D24" s="32" t="n">
         <v>7479.09</v>
       </c>
-      <c r="E24" s="33" t="n">
+      <c r="E24" s="32" t="n">
         <v>7479.09</v>
       </c>
-      <c r="F24" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="40" t="inlineStr">
+      <c r="F24" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="30" t="n">
+      <c r="A25" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="39" t="inlineStr">
+      <c r="B25" s="38" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C25" s="30" t="inlineStr">
+      <c r="C25" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D25" s="30" t="n">
+      <c r="D25" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="E25" s="30" t="n">
+      <c r="E25" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="F25" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="40" t="inlineStr">
+      <c r="F25" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="n">
+      <c r="A26" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="39" t="inlineStr">
+      <c r="B26" s="38" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
-      <c r="C26" s="30" t="inlineStr">
+      <c r="C26" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D26" s="33" t="n">
+      <c r="D26" s="32" t="n">
         <v>572.25</v>
       </c>
-      <c r="E26" s="33" t="n">
+      <c r="E26" s="32" t="n">
         <v>572.28</v>
       </c>
-      <c r="F26" s="33" t="n">
+      <c r="F26" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G26" s="40" t="inlineStr">
+      <c r="G26" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="30" t="n">
+      <c r="A27" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="39" t="inlineStr">
+      <c r="B27" s="38" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
-      <c r="C27" s="30" t="inlineStr">
+      <c r="C27" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D27" s="33" t="n">
+      <c r="D27" s="32" t="n">
         <v>11.45</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E27" s="32" t="n">
         <v>11.46</v>
       </c>
-      <c r="F27" s="33" t="n">
+      <c r="F27" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G27" s="40" t="inlineStr">
+      <c r="G27" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="30" t="n">
+      <c r="A28" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="39" t="inlineStr">
+      <c r="B28" s="38" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
-      <c r="C28" s="30" t="inlineStr">
+      <c r="C28" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D28" s="33" t="n">
+      <c r="D28" s="32" t="n">
         <v>572.25</v>
       </c>
-      <c r="E28" s="33" t="n">
+      <c r="E28" s="32" t="n">
         <v>572.25</v>
       </c>
-      <c r="F28" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="40" t="inlineStr">
+      <c r="F28" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="30" t="n">
+      <c r="A29" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="39" t="inlineStr">
+      <c r="B29" s="38" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
-      <c r="C29" s="30" t="inlineStr">
+      <c r="C29" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D29" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="33" t="n">
+      <c r="D29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="F29" s="33" t="n">
+      <c r="F29" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G29" s="41" t="inlineStr">
+      <c r="G29" s="40" t="inlineStr">
         <is>
           <t>EXPLAINED</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="30" t="n">
+      <c r="A30" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="39" t="inlineStr">
+      <c r="B30" s="38" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
-      <c r="C30" s="30" t="inlineStr">
+      <c r="C30" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="D30" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="40" t="inlineStr">
+      <c r="D30" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="30" t="n">
+      <c r="A31" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="39" t="inlineStr">
+      <c r="B31" s="38" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
-      <c r="C31" s="30" t="inlineStr">
+      <c r="C31" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D31" s="30" t="n">
+      <c r="D31" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="E31" s="30" t="n">
+      <c r="E31" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="F31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="40" t="inlineStr">
+      <c r="F31" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="30" t="n">
+      <c r="A32" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="39" t="inlineStr">
+      <c r="B32" s="38" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
-      <c r="C32" s="30" t="inlineStr">
+      <c r="C32" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D32" s="33" t="n">
+      <c r="D32" s="32" t="n">
         <v>13172.28</v>
       </c>
-      <c r="E32" s="33" t="n">
+      <c r="E32" s="32" t="n">
         <v>13172.28</v>
       </c>
-      <c r="F32" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="40" t="inlineStr">
+      <c r="F32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="n">
+      <c r="A33" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="39" t="inlineStr">
+      <c r="B33" s="38" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
-      <c r="C33" s="30" t="inlineStr">
+      <c r="C33" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D33" s="33" t="n">
+      <c r="D33" s="32" t="n">
         <v>627.28</v>
       </c>
-      <c r="E33" s="33" t="n">
+      <c r="E33" s="32" t="n">
         <v>627.28</v>
       </c>
-      <c r="F33" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="40" t="inlineStr">
+      <c r="F33" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="30" t="n">
+      <c r="A34" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="39" t="inlineStr">
+      <c r="B34" s="38" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
-      <c r="C34" s="30" t="inlineStr">
+      <c r="C34" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D34" s="33" t="n">
+      <c r="D34" s="32" t="n">
         <v>8193.67</v>
       </c>
-      <c r="E34" s="33" t="n">
+      <c r="E34" s="32" t="n">
         <v>8193.67</v>
       </c>
-      <c r="F34" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="40" t="inlineStr">
+      <c r="F34" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="n">
+      <c r="A35" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="39" t="inlineStr">
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
-      <c r="C35" s="30" t="inlineStr">
+      <c r="C35" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D35" s="33" t="n">
+      <c r="D35" s="32" t="n">
         <v>8023.46</v>
       </c>
-      <c r="E35" s="33" t="n">
+      <c r="E35" s="32" t="n">
         <v>8023.29</v>
       </c>
-      <c r="F35" s="33" t="n">
+      <c r="F35" s="32" t="n">
         <v>-0.17</v>
       </c>
-      <c r="G35" s="40" t="inlineStr">
+      <c r="G35" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="30" t="n">
+      <c r="A36" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="39" t="inlineStr">
+      <c r="B36" s="38" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
-      <c r="C36" s="30" t="inlineStr">
+      <c r="C36" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D36" s="33" t="n">
+      <c r="D36" s="32" t="n">
         <v>8023.46</v>
       </c>
-      <c r="E36" s="33" t="n">
+      <c r="E36" s="32" t="n">
         <v>8023.46</v>
       </c>
-      <c r="F36" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="40" t="inlineStr">
+      <c r="F36" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="30" t="n">
+      <c r="A37" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="39" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C37" s="30" t="inlineStr">
+      <c r="C37" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D37" s="33" t="n">
+      <c r="D37" s="32" t="n">
         <v>8023.46</v>
       </c>
-      <c r="E37" s="33" t="n">
+      <c r="E37" s="32" t="n">
         <v>8023.46</v>
       </c>
-      <c r="F37" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="40" t="inlineStr">
+      <c r="F37" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="30" t="n">
+      <c r="A38" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="39" t="inlineStr">
+      <c r="B38" s="38" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C38" s="30" t="inlineStr">
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D38" s="30" t="n">
+      <c r="D38" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="E38" s="30" t="n">
+      <c r="E38" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="F38" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="40" t="inlineStr">
+      <c r="F38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="30" t="n">
+      <c r="A39" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="39" t="inlineStr">
+      <c r="B39" s="38" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
-      <c r="C39" s="30" t="inlineStr">
+      <c r="C39" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D39" s="33" t="n">
+      <c r="D39" s="32" t="n">
         <v>627.25</v>
       </c>
-      <c r="E39" s="33" t="n">
+      <c r="E39" s="32" t="n">
         <v>627.28</v>
       </c>
-      <c r="F39" s="33" t="n">
+      <c r="F39" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G39" s="40" t="inlineStr">
+      <c r="G39" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n">
+      <c r="A40" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="39" t="inlineStr">
+      <c r="B40" s="38" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
-      <c r="C40" s="30" t="inlineStr">
+      <c r="C40" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D40" s="33" t="n">
+      <c r="D40" s="32" t="n">
         <v>12.54</v>
       </c>
-      <c r="E40" s="33" t="n">
+      <c r="E40" s="32" t="n">
         <v>12.54</v>
       </c>
-      <c r="F40" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="40" t="inlineStr">
+      <c r="F40" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="30" t="n">
+      <c r="A41" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="39" t="inlineStr">
+      <c r="B41" s="38" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
-      <c r="C41" s="30" t="inlineStr">
+      <c r="C41" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D41" s="33" t="n">
+      <c r="D41" s="32" t="n">
         <v>627.25</v>
       </c>
-      <c r="E41" s="33" t="n">
+      <c r="E41" s="32" t="n">
         <v>627.25</v>
       </c>
-      <c r="F41" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="40" t="inlineStr">
+      <c r="F41" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="n">
+      <c r="A42" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="39" t="inlineStr">
+      <c r="B42" s="38" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
-      <c r="C42" s="30" t="inlineStr">
+      <c r="C42" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D42" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="33" t="n">
+      <c r="D42" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="F42" s="33" t="n">
+      <c r="F42" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G42" s="41" t="inlineStr">
+      <c r="G42" s="40" t="inlineStr">
         <is>
           <t>EXPLAINED</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="n">
+      <c r="A43" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="39" t="inlineStr">
+      <c r="B43" s="38" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
-      <c r="C43" s="30" t="inlineStr">
+      <c r="C43" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="D43" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="40" t="inlineStr">
+      <c r="D43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="30" t="n">
+      <c r="A44" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="39" t="inlineStr">
+      <c r="B44" s="38" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
-      <c r="C44" s="30" t="inlineStr">
+      <c r="C44" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D44" s="30" t="n">
+      <c r="D44" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="E44" s="30" t="n">
+      <c r="E44" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="F44" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="40" t="inlineStr">
+      <c r="F44" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="30" t="n">
+      <c r="A45" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="39" t="inlineStr">
+      <c r="B45" s="38" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
-      <c r="C45" s="30" t="inlineStr">
+      <c r="C45" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D45" s="33" t="n">
+      <c r="D45" s="32" t="n">
         <v>4875.51</v>
       </c>
-      <c r="E45" s="33" t="n">
+      <c r="E45" s="32" t="n">
         <v>4875.51</v>
       </c>
-      <c r="F45" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="40" t="inlineStr">
+      <c r="F45" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="n">
+      <c r="A46" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="39" t="inlineStr">
+      <c r="B46" s="38" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
-      <c r="C46" s="30" t="inlineStr">
+      <c r="C46" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D46" s="33" t="n">
+      <c r="D46" s="32" t="n">
         <v>232.18</v>
       </c>
-      <c r="E46" s="33" t="n">
+      <c r="E46" s="32" t="n">
         <v>232.18</v>
       </c>
-      <c r="F46" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="40" t="inlineStr">
+      <c r="F46" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="30" t="n">
+      <c r="A47" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="39" t="inlineStr">
+      <c r="B47" s="38" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
-      <c r="C47" s="30" t="inlineStr">
+      <c r="C47" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D47" s="33" t="n">
+      <c r="D47" s="32" t="n">
         <v>3142.87</v>
       </c>
-      <c r="E47" s="33" t="n">
+      <c r="E47" s="32" t="n">
         <v>3142.87</v>
       </c>
-      <c r="F47" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" s="40" t="inlineStr">
+      <c r="F47" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="n">
+      <c r="A48" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="39" t="inlineStr">
+      <c r="B48" s="38" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
-      <c r="C48" s="30" t="inlineStr">
+      <c r="C48" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D48" s="33" t="n">
+      <c r="D48" s="32" t="n">
         <v>2972.66</v>
       </c>
-      <c r="E48" s="33" t="n">
+      <c r="E48" s="32" t="n">
         <v>2972.67</v>
       </c>
-      <c r="F48" s="33" t="n">
+      <c r="F48" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G48" s="40" t="inlineStr">
+      <c r="G48" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="30" t="n">
+      <c r="A49" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="39" t="inlineStr">
+      <c r="B49" s="38" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
-      <c r="C49" s="30" t="inlineStr">
+      <c r="C49" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D49" s="33" t="n">
+      <c r="D49" s="32" t="n">
         <v>2972.66</v>
       </c>
-      <c r="E49" s="33" t="n">
+      <c r="E49" s="32" t="n">
         <v>2972.66</v>
       </c>
-      <c r="F49" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="40" t="inlineStr">
+      <c r="F49" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="n">
+      <c r="A50" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="39" t="inlineStr">
+      <c r="B50" s="38" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C50" s="30" t="inlineStr">
+      <c r="C50" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D50" s="33" t="n">
+      <c r="D50" s="32" t="n">
         <v>2972.66</v>
       </c>
-      <c r="E50" s="33" t="n">
+      <c r="E50" s="32" t="n">
         <v>2972.66</v>
       </c>
-      <c r="F50" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="40" t="inlineStr">
+      <c r="F50" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="n">
+      <c r="A51" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="39" t="inlineStr">
+      <c r="B51" s="38" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C51" s="30" t="inlineStr">
+      <c r="C51" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D51" s="30" t="n">
+      <c r="D51" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="E51" s="30" t="n">
+      <c r="E51" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="F51" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="40" t="inlineStr">
+      <c r="F51" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="n">
+      <c r="A52" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="39" t="inlineStr">
+      <c r="B52" s="38" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
-      <c r="C52" s="30" t="inlineStr">
+      <c r="C52" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D52" s="33" t="n">
+      <c r="D52" s="32" t="n">
         <v>232.17</v>
       </c>
-      <c r="E52" s="33" t="n">
+      <c r="E52" s="32" t="n">
         <v>232.18</v>
       </c>
-      <c r="F52" s="33" t="n">
+      <c r="F52" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G52" s="40" t="inlineStr">
+      <c r="G52" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="30" t="n">
+      <c r="A53" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="39" t="inlineStr">
+      <c r="B53" s="38" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
-      <c r="C53" s="30" t="inlineStr">
+      <c r="C53" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D53" s="33" t="n">
+      <c r="D53" s="32" t="n">
         <v>4.64</v>
       </c>
-      <c r="E53" s="33" t="n">
+      <c r="E53" s="32" t="n">
         <v>4.65</v>
       </c>
-      <c r="F53" s="33" t="n">
+      <c r="F53" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G53" s="40" t="inlineStr">
+      <c r="G53" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="30" t="n">
+      <c r="A54" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="39" t="inlineStr">
+      <c r="B54" s="38" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
-      <c r="C54" s="30" t="inlineStr">
+      <c r="C54" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D54" s="33" t="n">
+      <c r="D54" s="32" t="n">
         <v>232.17</v>
       </c>
-      <c r="E54" s="33" t="n">
+      <c r="E54" s="32" t="n">
         <v>232.17</v>
       </c>
-      <c r="F54" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="40" t="inlineStr">
+      <c r="F54" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="n">
+      <c r="A55" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="39" t="inlineStr">
+      <c r="B55" s="38" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
-      <c r="C55" s="30" t="inlineStr">
+      <c r="C55" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D55" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="33" t="n">
+      <c r="D55" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="F55" s="33" t="n">
+      <c r="F55" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G55" s="40" t="inlineStr">
+      <c r="G55" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="30" t="n">
+      <c r="A56" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="39" t="inlineStr">
+      <c r="B56" s="38" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
-      <c r="C56" s="30" t="inlineStr">
+      <c r="C56" s="31" t="inlineStr">
         <is>
           <t>20–26 Sep 2026</t>
         </is>
       </c>
-      <c r="D56" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="40" t="inlineStr">
+      <c r="D56" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="30" t="n">
+      <c r="A57" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="39" t="inlineStr">
+      <c r="B57" s="38" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
-      <c r="C57" s="30" t="inlineStr">
+      <c r="C57" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D57" s="30" t="n">
+      <c r="D57" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="E57" s="30" t="n">
+      <c r="E57" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="F57" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="40" t="inlineStr">
+      <c r="F57" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="30" t="n">
+      <c r="A58" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="39" t="inlineStr">
+      <c r="B58" s="38" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
-      <c r="C58" s="30" t="inlineStr">
+      <c r="C58" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D58" s="33" t="n">
+      <c r="D58" s="32" t="n">
         <v>7476</v>
       </c>
-      <c r="E58" s="33" t="n">
+      <c r="E58" s="32" t="n">
         <v>7476</v>
       </c>
-      <c r="F58" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="40" t="inlineStr">
+      <c r="F58" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="30" t="n">
+      <c r="A59" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="39" t="inlineStr">
+      <c r="B59" s="38" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
-      <c r="C59" s="30" t="inlineStr">
+      <c r="C59" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D59" s="33" t="n">
+      <c r="D59" s="32" t="n">
         <v>356</v>
       </c>
-      <c r="E59" s="33" t="n">
+      <c r="E59" s="32" t="n">
         <v>356</v>
       </c>
-      <c r="F59" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="40" t="inlineStr">
+      <c r="F59" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="30" t="n">
+      <c r="A60" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="39" t="inlineStr">
+      <c r="B60" s="38" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
-      <c r="C60" s="30" t="inlineStr">
+      <c r="C60" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D60" s="33" t="n">
+      <c r="D60" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="E60" s="33" t="n">
+      <c r="E60" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="F60" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="40" t="inlineStr">
+      <c r="F60" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="n">
+      <c r="A61" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="39" t="inlineStr">
+      <c r="B61" s="38" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
-      <c r="C61" s="30" t="inlineStr">
+      <c r="C61" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D61" s="33" t="n">
+      <c r="D61" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="E61" s="33" t="n">
+      <c r="E61" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="F61" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="40" t="inlineStr">
+      <c r="F61" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="n">
+      <c r="A62" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="39" t="inlineStr">
+      <c r="B62" s="38" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
-      <c r="C62" s="30" t="inlineStr">
+      <c r="C62" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D62" s="33" t="n">
+      <c r="D62" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="E62" s="33" t="n">
+      <c r="E62" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="F62" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="40" t="inlineStr">
+      <c r="F62" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="n">
+      <c r="A63" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="39" t="inlineStr">
+      <c r="B63" s="38" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C63" s="30" t="inlineStr">
+      <c r="C63" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D63" s="33" t="n">
+      <c r="D63" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="E63" s="33" t="n">
+      <c r="E63" s="32" t="n">
         <v>4819.24</v>
       </c>
-      <c r="F63" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="40" t="inlineStr">
+      <c r="F63" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="n">
+      <c r="A64" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="39" t="inlineStr">
+      <c r="B64" s="38" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
-      <c r="C64" s="30" t="inlineStr">
+      <c r="C64" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D64" s="30" t="n">
+      <c r="D64" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="E64" s="30" t="n">
+      <c r="E64" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="F64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="40" t="inlineStr">
+      <c r="F64" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="30" t="n">
+      <c r="A65" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="39" t="inlineStr">
+      <c r="B65" s="38" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
-      <c r="C65" s="30" t="inlineStr">
+      <c r="C65" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D65" s="33" t="n">
+      <c r="D65" s="32" t="n">
         <v>356</v>
       </c>
-      <c r="E65" s="33" t="n">
+      <c r="E65" s="32" t="n">
         <v>356</v>
       </c>
-      <c r="F65" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="40" t="inlineStr">
+      <c r="F65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="30" t="n">
+      <c r="A66" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="39" t="inlineStr">
+      <c r="B66" s="38" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
-      <c r="C66" s="30" t="inlineStr">
+      <c r="C66" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D66" s="33" t="n">
+      <c r="D66" s="32" t="n">
         <v>7.12</v>
       </c>
-      <c r="E66" s="33" t="n">
+      <c r="E66" s="32" t="n">
         <v>7.12</v>
       </c>
-      <c r="F66" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="40" t="inlineStr">
+      <c r="F66" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="30" t="n">
+      <c r="A67" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="39" t="inlineStr">
+      <c r="B67" s="38" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C67" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D67" s="33" t="n">
+      <c r="D67" s="32" t="n">
         <v>356</v>
       </c>
-      <c r="E67" s="33" t="n">
+      <c r="E67" s="32" t="n">
         <v>356</v>
       </c>
-      <c r="F67" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="40" t="inlineStr">
+      <c r="F67" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="30" t="n">
+      <c r="A68" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="39" t="inlineStr">
+      <c r="B68" s="38" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
-      <c r="C68" s="30" t="inlineStr">
+      <c r="C68" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D68" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="40" t="inlineStr">
+      <c r="D68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="n">
+      <c r="A69" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="39" t="inlineStr">
+      <c r="B69" s="38" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C69" s="31" t="inlineStr">
         <is>
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="40" t="inlineStr">
+      <c r="D69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="n">
+      <c r="A70" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="39" t="inlineStr">
+      <c r="B70" s="38" t="inlineStr">
+        <is>
+          <t>Compensation + un-compensated deduction = amount paid by the customer</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>01–05 Sep 2026 · 247576408124202</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="38" t="inlineStr">
+        <is>
+          <t>Compensation + un-compensated value = net bill value</t>
+        </is>
+      </c>
+      <c r="C71" s="31" t="inlineStr">
+        <is>
+          <t>01–05 Sep 2026 · 247576408124202</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>590</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>590</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="38" t="inlineStr">
+        <is>
+          <t>Complaint &amp; cancellation charges = 20% of net bill value + 5% GST (₹118.00 × 1.05)</t>
+        </is>
+      </c>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>01–05 Sep 2026 · 247576408124202</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="38" t="inlineStr">
+        <is>
+          <t>GST collected = GST discharged + GST on the un-compensated 20%</t>
+        </is>
+      </c>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>01–05 Sep 2026 · 247576408124202</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G73" s="39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="38" t="inlineStr">
+        <is>
+          <t>Restaurant-cancelled order: no supply, no GST discharged on the food</t>
+        </is>
+      </c>
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>06–12 Sep 2026 · 248201907107833</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="38" t="inlineStr">
+        <is>
+          <t>Restaurant-cancelled order: no supply, no GST discharged on the food</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>13–19 Sep 2026 · 248773805195420</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="31" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="38" t="inlineStr">
+        <is>
+          <t>Month: complaint &amp; cancellation charges (payout line C) = un-compensated 20% + 5% GST</t>
+        </is>
+      </c>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>All cycles</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="E76" s="32" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="39" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="31" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="38" t="inlineStr">
         <is>
           <t>Month: GST discharged = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
-      <c r="C70" s="30" t="inlineStr">
+      <c r="C77" s="31" t="inlineStr">
         <is>
           <t>All cycles</t>
         </is>
       </c>
-      <c r="D70" s="33" t="n">
+      <c r="D77" s="32" t="n">
         <v>2305.92</v>
       </c>
-      <c r="E70" s="33" t="n">
+      <c r="E77" s="32" t="n">
         <v>2305.92</v>
       </c>
-      <c r="F70" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="40" t="inlineStr">
+      <c r="F77" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="30" t="n">
-        <v>67</v>
-      </c>
-      <c r="B71" s="39" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="31" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="38" t="inlineStr">
         <is>
           <t>Month: residual GST difference after the cancellation policy (pure paise rounding)</t>
         </is>
       </c>
-      <c r="C71" s="30" t="inlineStr">
+      <c r="C78" s="31" t="inlineStr">
         <is>
           <t>All cycles</t>
         </is>
       </c>
-      <c r="D71" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="33" t="n">
+      <c r="D78" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="32" t="n">
         <v>0.12</v>
       </c>
-      <c r="F71" s="33" t="n">
+      <c r="F78" s="32" t="n">
         <v>0.12</v>
       </c>
-      <c r="G71" s="40" t="inlineStr">
+      <c r="G78" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="30" t="n">
-        <v>68</v>
-      </c>
-      <c r="B72" s="39" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="31" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="38" t="inlineStr">
         <is>
           <t>Order-wise net payout = customer paid − Swiggy fees − complaint/cancellation − taxes</t>
         </is>
       </c>
-      <c r="C72" s="30" t="inlineStr">
+      <c r="C79" s="31" t="inlineStr">
         <is>
           <t>All 95 orders</t>
         </is>
       </c>
-      <c r="D72" s="30" t="inlineStr">
+      <c r="D79" s="31" t="inlineStr">
         <is>
           <t>0 exceptions</t>
         </is>
       </c>
-      <c r="E72" s="30" t="inlineStr">
+      <c r="E79" s="31" t="inlineStr">
         <is>
           <t>0 exceptions</t>
         </is>
       </c>
-      <c r="F72" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G72" s="40" t="inlineStr">
+      <c r="F79" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="30" t="n">
-        <v>69</v>
-      </c>
-      <c r="B73" s="39" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="31" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="38" t="inlineStr">
         <is>
           <t>Highest paise-level rounding inside the annexures (tolerated, not adjusted)</t>
         </is>
       </c>
-      <c r="C73" s="30" t="inlineStr">
+      <c r="C80" s="31" t="inlineStr">
         <is>
           <t>All orders</t>
         </is>
       </c>
-      <c r="D73" s="30" t="inlineStr">
+      <c r="D80" s="31" t="inlineStr">
         <is>
           <t>≤ ₹0.05</t>
         </is>
       </c>
-      <c r="E73" s="30" t="inlineStr">
+      <c r="E80" s="31" t="inlineStr">
         <is>
           <t>₹0.03</t>
         </is>
       </c>
-      <c r="F73" s="30" t="n"/>
-      <c r="G73" s="40" t="inlineStr">
+      <c r="F80" s="31" t="n"/>
+      <c r="G80" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="B74" s="39" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="31" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="38" t="inlineStr">
         <is>
           <t>Duplicate Order IDs across payout cycles</t>
         </is>
       </c>
-      <c r="C74" s="30" t="inlineStr">
+      <c r="C81" s="31" t="inlineStr">
         <is>
           <t>All cycles</t>
         </is>
       </c>
-      <c r="D74" s="30" t="inlineStr">
+      <c r="D81" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G74" s="40" t="inlineStr">
+      <c r="E81" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="30" t="n">
-        <v>71</v>
-      </c>
-      <c r="B75" s="39" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="31" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="38" t="inlineStr">
         <is>
           <t>Payout cycles are continuous with no gap/overlap</t>
         </is>
       </c>
-      <c r="C75" s="30" t="inlineStr">
+      <c r="C82" s="31" t="inlineStr">
         <is>
           <t>01–30 Sep 2026</t>
         </is>
       </c>
-      <c r="D75" s="30" t="inlineStr">
+      <c r="D82" s="31" t="inlineStr">
         <is>
           <t>0 gaps</t>
         </is>
       </c>
-      <c r="E75" s="30" t="inlineStr">
+      <c r="E82" s="31" t="inlineStr">
         <is>
           <t>0 gaps</t>
         </is>
       </c>
-      <c r="F75" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G75" s="40" t="inlineStr">
+      <c r="F82" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="30" t="n">
-        <v>72</v>
-      </c>
-      <c r="B76" s="39" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="31" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="38" t="inlineStr">
         <is>
           <t>Coverage of the month</t>
         </is>
       </c>
-      <c r="C76" s="30" t="inlineStr">
+      <c r="C83" s="31" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="D76" s="30" t="inlineStr">
+      <c r="D83" s="31" t="inlineStr">
         <is>
           <t>01 Sep 2026</t>
         </is>
       </c>
-      <c r="E76" s="30" t="inlineStr">
+      <c r="E83" s="31" t="inlineStr">
         <is>
           <t>01 Sep 2026</t>
         </is>
       </c>
-      <c r="F76" s="30" t="n"/>
-      <c r="G76" s="40" t="inlineStr">
+      <c r="F83" s="31" t="n"/>
+      <c r="G83" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="30" t="n">
-        <v>73</v>
-      </c>
-      <c r="B77" s="39" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="31" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="38" t="inlineStr">
         <is>
           <t>Coverage of the month — end</t>
         </is>
       </c>
-      <c r="C77" s="30" t="inlineStr">
+      <c r="C84" s="31" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="D77" s="30" t="inlineStr">
+      <c r="D84" s="31" t="inlineStr">
         <is>
           <t>30 Sep 2026</t>
         </is>
       </c>
-      <c r="E77" s="30" t="inlineStr">
+      <c r="E84" s="31" t="inlineStr">
         <is>
           <t>30 Sep 2026</t>
         </is>
       </c>
-      <c r="F77" s="30" t="n"/>
-      <c r="G77" s="40" t="inlineStr">
+      <c r="F84" s="31" t="n"/>
+      <c r="G84" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="30" t="n">
-        <v>74</v>
-      </c>
-      <c r="B78" s="39" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="31" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="38" t="inlineStr">
         <is>
           <t>Unresolved customer complaints outstanding</t>
         </is>
       </c>
-      <c r="C78" s="30" t="inlineStr">
+      <c r="C85" s="31" t="inlineStr">
         <is>
           <t>All cycles</t>
         </is>
       </c>
-      <c r="D78" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" s="40" t="inlineStr">
+      <c r="D85" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="39" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="B80" s="5" t="inlineStr">
+    <row r="86"/>
+    <row r="87">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>Exceptions requiring attention</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="B81" s="42" t="inlineStr">
+    <row r="88" ht="30" customHeight="1">
+      <c r="B88" s="41" t="inlineStr">
         <is>
           <t>•  GST discharged by Swiggy (₹2,305.92) is ₹6.02 lower than the GST billed to customers (₹2,311.94). This is CORRECT and not a discrepancy: ₹5.90 of it is the effect of the cancellation-compensation policy (order 247576408124202 in the 01–05 Sep cycle was cancelled before pickup and is compensated at 80% of the order value, so GST was discharged on ₹472.00 instead of ₹590.00), and the remaining ₹0.12 is paise rounding on the other orders. See the 'Cancelled Orders' sheet and the GST working workbook → Sec 9(5) Reconciliation.</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1">
-      <c r="B82" s="42" t="inlineStr">
+    <row r="89" ht="30" customHeight="1">
+      <c r="B89" s="41" t="inlineStr">
         <is>
           <t>•  The 20–26 Sep cycle's annexure is generated on 01 Oct and the 27–30 Sep cycle is a four-day cycle — payout cycles are not equal length, so compare rates (not totals) across cycles.</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="30" customHeight="1">
-      <c r="B83" s="42" t="inlineStr">
+    <row r="90" ht="30" customHeight="1">
+      <c r="B90" s="41" t="inlineStr">
         <is>
           <t>•  Ads investments of ₹680.84 were recovered in 4 of the 5 cycles against 'Aug-26' ad packs (₹170.21 per cycle: Top Picks ₹110.62 + Ads Offers ₹59.59), and nil in the 27–30 Sep cycle.</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="B84" s="42" t="inlineStr">
+    <row r="91" ht="30" customHeight="1">
+      <c r="B91" s="41" t="inlineStr">
         <is>
           <t>•  The Discount Summary sheet in every annexure says 'Unable to fetch Campaign Details' — Swiggy has not given the coupon-level discount breakdown even though 8–21 orders per cycle carried a discount code (75 orders across the month).</t>
         </is>
       </c>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="B85" s="42" t="inlineStr">
+    <row r="92" ht="30" customHeight="1">
+      <c r="B92" s="41" t="inlineStr">
         <is>
           <t>•  Differences of a few paise on the payout equations are Swiggy's own rounding inside the annexures (the same cycle shows a paise difference between its delivered/cancelled columns and its total column); they are disclosed here rather than adjusted.</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="18" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="18" t="inlineStr">
         <is>
           <t>Source: Swiggy weekly payout annexures · Prepared 05 October 2026</t>
         </is>
@@ -3246,11 +3444,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B81:G81"/>
-    <mergeCell ref="B85:G85"/>
-    <mergeCell ref="B84:G84"/>
-    <mergeCell ref="B83:G83"/>
-    <mergeCell ref="B82:G82"/>
+    <mergeCell ref="B89:G89"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="B88:G88"/>
+    <mergeCell ref="B92:G92"/>
+    <mergeCell ref="B91:G91"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3302,405 +3500,405 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="35" t="n">
+      <c r="A5" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Item Total</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t>Total value of ordered items (without taxes)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="35" t="n">
+      <c r="A6" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="33" t="inlineStr">
         <is>
           <t>Packaging Charges</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="33" t="inlineStr">
         <is>
           <t>Total amount paid for packaging (without taxes)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="n">
+      <c r="A7" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Restaurant Item Discount</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>Total discounts on like SWIGGYIT, FLATDEAL and other item level discounts sponsored by the restaurant.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="n">
+      <c r="A8" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Swiggy One extra discount</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>Additional discount sponsored by the restaurant for orders placed by Swiggy One customers</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="n">
+      <c r="A9" s="33" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Discount Share</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>Total discounts on items sponsored by the Restaurant</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n">
+      <c r="A10" s="33" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Net Bill Value (Before Taxes)</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>Total sales amount including item total, packaging charges and restaurant sponsored discounts before GST</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n">
+      <c r="A11" s="33" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>GST Collected</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>GST collected from the customer on behalf of the restaurant</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n">
+      <c r="A12" s="33" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Delivery Fee</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>Delivery Fee before taxes charged by the self delivery restaurant collected from the customer</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="33" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Discount on Delivery Fee</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>Discount on Delivery Fee offered by the self delivery restaurant</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n">
+      <c r="A14" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>GST on Delivery Fee</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>GST charged on the Delivery Fees by the restaurant collected from the customer</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="33" t="inlineStr">
         <is>
           <t>Commission charged on</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="33" t="inlineStr">
         <is>
           <t>Commissionable value on which the base commission is charged on the order</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n">
+      <c r="A16" s="33" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="33" t="inlineStr">
         <is>
           <t>Commission %</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="33" t="inlineStr">
         <is>
           <t>Base commission percentage as per the agreement between restaurant and Swiggy</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="n">
+      <c r="A17" s="33" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="33" t="inlineStr">
         <is>
           <t>Commission</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="33" t="inlineStr">
         <is>
           <t>Commission collected as service fee by Swiggy on the order value</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n">
+      <c r="A18" s="33" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="33" t="inlineStr">
         <is>
           <t>Long Distance Charges</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="33" t="inlineStr">
         <is>
           <t>Total amount collected for long distance orders</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n">
+      <c r="A19" s="33" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="33" t="inlineStr">
         <is>
           <t>Pocket Hero Fees</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="33" t="inlineStr">
         <is>
           <t>Amount collected for orders placed under the Pocket Hero program</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n">
+      <c r="A20" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="33" t="inlineStr">
         <is>
           <t>Swiggy One Fees</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="33" t="inlineStr">
         <is>
           <t>Amount collected for orders placed by Swiggy One customers as per the agreed policy</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n">
+      <c r="A21" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="33" t="inlineStr">
         <is>
           <t>Bolt Fees</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="33" t="inlineStr">
         <is>
           <t>Charged for Bolt orders</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="n">
+      <c r="A22" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="33" t="inlineStr">
         <is>
           <t>Payment Collection Charges</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="33" t="inlineStr">
         <is>
           <t>Amount charged for online payment mechanisms</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="n">
+      <c r="A23" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="33" t="inlineStr">
         <is>
           <t>Restaurant Cancellation Charges</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="33" t="inlineStr">
         <is>
           <t>Amount charged for orders cancelled by the restaurant as per the agreed terms</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="n">
+      <c r="A24" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="33" t="inlineStr">
         <is>
           <t>Call Center Charges</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="33" t="inlineStr">
         <is>
           <t>Amount charged for IVR calls made as reminders for delayed order acceptance</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="n">
+      <c r="A25" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="33" t="inlineStr">
         <is>
           <t>Delivery Fee sponsored by Restaurant</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="33" t="inlineStr">
         <is>
           <t>Delivery charges paid by the restaurant partner on behalf of the customer as agreed campaign terms</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="n">
+      <c r="A26" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="33" t="inlineStr">
         <is>
           <t>GST on Swiggy Fees [9+10-11+12+13+14+15+16+17]*18%</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="33" t="inlineStr">
         <is>
           <t>GST amount collected on Swiggy Fees</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="n">
+      <c r="A27" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="33" t="inlineStr">
         <is>
           <t>Customer Cancellations</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="33" t="inlineStr">
         <is>
           <t>Amount collected for orders cancelled by customers as per the payment terms for the partner</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="n">
+      <c r="A28" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="33" t="inlineStr">
         <is>
           <t>Customer Complaints</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="33" t="inlineStr">
         <is>
           <t>Refunds paid to the customer for food related issues</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="n">
+      <c r="A29" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="33" t="inlineStr">
         <is>
           <t>GST paid by Swiggy on behalf of restaurant - under section 9(5)</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="33" t="inlineStr">
         <is>
           <t>Tax amount retained by Swiggy for restaurant services as per Section 9(5) of GST Act 2017, with effect from 1 January 2022. Swiggy deposits this tax amount with authorities on behalf of the restaurant.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="n">
+      <c r="A30" s="33" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C30" s="33" t="inlineStr">
         <is>
           <t>TCS is amount collected at source by Swiggy on items other than Restaurant Services in terms of provisions of Section 52 of the CGST Act, 2017. The said amount will be deposited to Government upon filing of TCS Return {GSTR-8} at GSTIN level.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="n">
+      <c r="A31" s="33" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="33" t="inlineStr">
         <is>
           <t>TDS</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="33" t="inlineStr">
         <is>
           <t>Swiggy is required to deduct taxes at source from the amount for all Orders that are settled via Swiggy. TDS u/s 194-O shall be applied on Gross Sales (less applicable taxes charged by the Restaurant) as per the applicable tax law on the rate as applicable and amended from time to time.</t>
         </is>
@@ -3714,21 +3912,21 @@
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="42" t="inlineStr">
+      <c r="A34" s="41" t="inlineStr">
         <is>
           <t>•  In the Order Level sheet, 'Total Swiggy Fees' is inclusive of the 18% GST charged on Swiggy's own service fee.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="42" t="inlineStr">
+      <c r="A35" s="41" t="inlineStr">
         <is>
           <t>•  In the Payout Breakup, 'Swiggy Fees' (line B) excludes that GST — it appears separately as line 19 'GST on Service Fee @18%'. The payout equation A+B+C+D+E+F=G therefore ties only with the payout-breakup convention.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="42" t="inlineStr">
+      <c r="A36" s="41" t="inlineStr">
         <is>
           <t>•  'GST Deduction' (line 18) is the 5% GST on the food supply that Swiggy retains and deposits under Section 9(5) of the CGST Act — it is not a charge on the restaurant.</t>
         </is>
@@ -16315,97 +16513,95 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="60" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>Cancelled orders &amp; the 80% compensation policy</t>
+          <t>Cancelled orders — the 80% compensation policy</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>How a pre-pickup cancellation changes the value on which GST and TDS are computed</t>
+          <t>Every rupee of a pre-pickup cancellation accounted for: value, GST and the deduction</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Swiggy's policy: "Order cancelled before pickup — as per policy, you will be paid 80% less commissions as compensation."</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>The restaurant is therefore taxed on the 80% compensation, not on the full value the customer had paid. Derived basis:</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>The restaurant is taxed on the 80% compensation, not on the full value the customer had paid, and the un-compensated 20%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        compensation value (pre-tax) = 80% × net bill value      →  590.00 × 80% = 472.00</t>
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>is deducted from the payout as a GST-inclusive amount. For order 247576408124202 (net bill value ₹590.00):</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        GST discharged u/s 9(5)      = 5% × compensation value  →  472.00 × 5% = 23.60</t>
+          <t xml:space="preserve">        compensation  80% × 590.00 = 472.00   + GST 5% 23.60  =  495.60  → credited (commission is charged on this)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        TDS u/s 194-O                = 0.1% × compensation value→  472.00 × 0.1% = 0.47</t>
+          <t xml:space="preserve">        un-compensated 20% × 590.00 = 118.00  + GST 5%  5.90  =  123.90  → 'Complaint &amp; Cancellation Charges [18+19]'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        commission / collection      = charged on 80% × amount paid by customer  →  619.50 × 80% = 495.60</t>
+          <t xml:space="preserve">        ---------------------------------------------------------------------------------------------------------</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        un-compensated 20%           = 619.50 × 20% = 123.90   →  reported as 'Customer Cancellations'</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>An order cancelled BY THE RESTAURANT earns no compensation: no supply, no GST, only the cancellation charge.</t>
+          <t xml:space="preserve">        net bill value 590.00 + GST 29.50 = 619.50 paid by the customer = 495.60 + 123.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>A.  Cancelled before pickup (not by the restaurant) — compensated at 80%</t>
         </is>
       </c>
     </row>
@@ -16422,67 +16618,67 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Order date</t>
+          <t>Cancelled by</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Cancelled by</t>
+          <t>Net bill value</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Pickup status</t>
+          <t>GST collected</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>Cancel time (min)</t>
+          <t>Paid by customer</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Order value (net bill)</t>
+          <t>Compensation 80% (pre-tax)</t>
         </is>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>GST collected</t>
+          <t>GST @5% on compensation</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>Paid by customer</t>
+          <t>Compensation received (incl. GST)</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Compensation %</t>
+          <t>Un-compensated 20% (pre-tax)</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Compensation value (pre-tax)</t>
+          <t>GST @5% on the un-compensated 20%</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>Compensation incl. GST</t>
+          <t>Complaint &amp; cancellation charges deducted (GST-inclusive)</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>GST @5% on compensation</t>
+          <t>Per annexure</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>GST deducted per annexure</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>Difference</t>
+          <t>Check: compensation + deduction = paid by customer</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
@@ -16495,322 +16691,464 @@
           <t>TDS per annexure</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>Restaurant cancellation charge</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>Basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>01–05 Sep 2026</t>
         </is>
       </c>
-      <c r="B14" s="30" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>247576408124202</t>
         </is>
       </c>
-      <c r="C14" s="31" t="n">
-        <v>46270.69685185186</v>
-      </c>
-      <c r="D14" s="30" t="inlineStr">
-        <is>
-          <t>SWIGGY</t>
-        </is>
-      </c>
-      <c r="E14" s="30" t="inlineStr">
-        <is>
-          <t>not picked up</t>
-        </is>
-      </c>
-      <c r="F14" s="32" t="n">
-        <v>52.25</v>
-      </c>
-      <c r="G14" s="33" t="n">
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Swiggy</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>590</v>
       </c>
-      <c r="H14" s="33" t="n">
+      <c r="E14" s="10" t="n">
         <v>29.5</v>
       </c>
-      <c r="I14" s="33" t="n">
+      <c r="F14" s="10" t="n">
         <v>619.5</v>
       </c>
-      <c r="J14" s="34" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K14" s="33" t="n">
+      <c r="G14" s="10" t="n">
         <v>472</v>
       </c>
-      <c r="L14" s="33" t="n">
+      <c r="H14" s="10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I14" s="10" t="n">
         <v>495.6</v>
       </c>
-      <c r="M14" s="33" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="N14" s="33" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="O14" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="33" t="n">
+      <c r="J14" s="10" t="n">
+        <v>118</v>
+      </c>
+      <c r="K14" s="10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L14" s="30" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="M14" s="10" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="N14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="10" t="n">
+        <v>619.5</v>
+      </c>
+      <c r="P14" s="10" t="n">
         <v>0.47</v>
       </c>
-      <c r="Q14" s="33" t="n">
+      <c r="Q14" s="10" t="n">
         <v>0.47</v>
       </c>
-      <c r="R14" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="35" t="inlineStr">
-        <is>
-          <t>Cancelled by Swiggy before pickup — compensated at 80% of the order value; GST and TDS computed on the compensation value</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="30" t="inlineStr">
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>B.  Cancelled by the restaurant — no compensation, no supply, no GST on the food</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Payout period</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>Order ID</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Restaurant cancellation charge (excl. GST)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>GST @18% on the charge</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Total recovered by Swiggy</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>GST discharged u/s 9(5) on the food</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Net payout</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>Remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="31" t="inlineStr">
         <is>
           <t>06–12 Sep 2026</t>
         </is>
       </c>
-      <c r="B15" s="30" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>248201907107833</t>
         </is>
       </c>
-      <c r="C15" s="31" t="n">
-        <v>46277.93642361111</v>
-      </c>
-      <c r="D15" s="30" t="inlineStr">
-        <is>
-          <t>MERCHANT</t>
-        </is>
-      </c>
-      <c r="E15" s="30" t="inlineStr">
-        <is>
-          <t>not picked up</t>
-        </is>
-      </c>
-      <c r="F15" s="32" t="n">
-        <v>113.5333333333333</v>
-      </c>
-      <c r="G15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="33" t="n">
+      <c r="C18" s="32" t="n">
         <v>82.5</v>
       </c>
-      <c r="S15" s="35" t="inlineStr">
-        <is>
-          <t>Cancelled by Merchant — no compensation and no supply; only the restaurant cancellation charge and GST on Swiggy's fee apply</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="D18" s="32" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="E18" s="32" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="F18" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="32" t="n">
+        <v>-97.34999999999999</v>
+      </c>
+      <c r="H18" s="33" t="inlineStr">
+        <is>
+          <t>No supply — the restaurant keeps nothing and pays the cancellation charge; no GST arises on the food</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>13–19 Sep 2026</t>
         </is>
       </c>
-      <c r="B16" s="30" t="inlineStr">
+      <c r="B19" s="31" t="inlineStr">
         <is>
           <t>248773805195420</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n">
-        <v>46284.55561342592</v>
-      </c>
-      <c r="D16" s="30" t="inlineStr">
-        <is>
-          <t>MERCHANT</t>
-        </is>
-      </c>
-      <c r="E16" s="30" t="inlineStr">
-        <is>
-          <t>not picked up</t>
-        </is>
-      </c>
-      <c r="F16" s="32" t="n">
-        <v>4.766666666666667</v>
-      </c>
-      <c r="G16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="33" t="n">
+      <c r="C19" s="32" t="n">
         <v>252.25</v>
       </c>
-      <c r="S16" s="35" t="inlineStr">
-        <is>
-          <t>Cancelled by Merchant — no compensation and no supply; only the restaurant cancellation charge and GST on Swiggy's fee apply</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>ALL CANCELLED ORDERS</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n"/>
-      <c r="C17" s="15" t="n"/>
-      <c r="D17" s="15" t="n"/>
-      <c r="E17" s="15" t="n"/>
-      <c r="F17" s="15" t="n"/>
-      <c r="G17" s="17" t="n">
-        <v>590</v>
-      </c>
-      <c r="H17" s="17" t="n"/>
-      <c r="I17" s="17" t="n"/>
-      <c r="J17" s="15" t="n"/>
-      <c r="K17" s="17" t="n"/>
-      <c r="L17" s="17" t="n"/>
-      <c r="M17" s="17" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="N17" s="17" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="O17" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" s="17" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="Q17" s="17" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="R17" s="17" t="n">
-        <v>334.75</v>
-      </c>
-      <c r="S17" s="15" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>Effect on the month's GST (see the GST working workbook → Sec 9(5) Reconciliation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Billed value of all orders                     : ₹46,236.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Less: un-compensated 20% of the cancelled order: ₹118.00</t>
+      <c r="D19" s="32" t="n">
+        <v>45.4</v>
+      </c>
+      <c r="E19" s="32" t="n">
+        <v>297.65</v>
+      </c>
+      <c r="F19" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="32" t="n">
+        <v>-297.65</v>
+      </c>
+      <c r="H19" s="33" t="inlineStr">
+        <is>
+          <t>No supply — the restaurant keeps nothing and pays the cancellation charge; no GST arises on the food</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>GST-reportable value (billed − adjustment)     : ₹46,118.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>GST @5% on the reportable value                : ₹2,305.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>GST actually discharged by Swiggy              : ₹2,305.92   →  agrees to the paisa</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
-        <is>
-          <t>Policy basis: Swiggy compensates a pre-pickup cancellation (not caused by the restaurant) at 80% of the order value; GST u/s 9(5) and TDS u/s 194-O are computed on that compensation value. Figures verified order by order against the annexures.</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>C.  How this maps to the annexure columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Annexure column</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Value for order 247576408124202</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>Net Bill Value (before taxes) [1+2-3]</t>
+        </is>
+      </c>
+      <c r="B24" s="33" t="inlineStr">
+        <is>
+          <t>590.00</t>
+        </is>
+      </c>
+      <c r="C24" s="33" t="inlineStr">
+        <is>
+          <t>Order value, exclusive of GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>GST Collected</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>29.50</t>
+        </is>
+      </c>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>5% charged to the customer on ₹590.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>Total Customer Paid [4+5]</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>619.50</t>
+        </is>
+      </c>
+      <c r="C26" s="33" t="inlineStr">
+        <is>
+          <t>What the customer actually paid</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Commission charged on</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>495.60</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>80% × ₹619.50 — commission is charged on the compensation, not the full order</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>GST Deduction</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>23.60</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="inlineStr">
+        <is>
+          <t>5% × ₹472.00 — tax discharged u/s 9(5) on the compensation value only</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
+        <is>
+          <t>Customer Cancellations / Complaint &amp; Cancellation Charges [18+19]</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="inlineStr">
+        <is>
+          <t>123.90</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>Un-compensated 20% (₹118.00) + GST @5% on it (₹5.90) — a GST-inclusive deduction</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
+          <t>TDS</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="inlineStr">
+        <is>
+          <t>0.1% × ₹472.00 — TDS on the compensation value only</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>D.  Effect on the month's GST</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Billed value of all orders</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>46236.33</v>
+      </c>
+      <c r="C33" s="33" t="inlineStr">
+        <is>
+          <t>Full value shown to customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Less: un-compensated 20% of the cancelled order (pre-tax)</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>-118</v>
+      </c>
+      <c r="C34" s="33" t="inlineStr">
+        <is>
+          <t>₹590.00 × 20% — the value is not a supply because the restaurant was compensated at 80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>GST-reportable value</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>46118.33</v>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>Value on which the 5% GST is discharged u/s 9(5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>GST discharged by Swiggy</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>2305.92</v>
+      </c>
+      <c r="C36" s="33">
+        <f> 5% × the reportable value — agrees to the paisa</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>GST collected from customers on the full billed value</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>2311.94</v>
+      </c>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>5% × ₹46,236.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Less: GST on the un-compensated 20%, deducted inside the ₹123.90 cancellation charge</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="C38" s="33" t="inlineStr">
+        <is>
+          <t>₹118.00 × 5% — this GST is not payable and is deducted from the payout along with the value</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Less: paise rounding inside the annexures</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="C39" s="33" t="inlineStr">
+        <is>
+          <t>Each order's GST is rounded to the nearest paisa</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>GST discharged by Swiggy — after the two adjustments above</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>2305.92</v>
+      </c>
+      <c r="C40" s="34" t="inlineStr">
+        <is>
+          <t>Ties the total GST billed to customers to the total GST discharged</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Policy basis: Swiggy compensates a pre-pickup cancellation (not caused by the restaurant) at 80% of the order value; GST u/s 9(5) and TDS u/s 194-O are computed on that compensation value, and the un-compensated 20% is deducted inclusive of its 5% GST. Verified order by order against the annexures.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A6:H6"/>
+  <mergeCells count="7">
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A10:J10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16932,7 +17270,7 @@
           <t>260909FS24001458</t>
         </is>
       </c>
-      <c r="I5" s="35" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t>Deduction 1 of Ads Offers - Ads Growth Pack - Aug'26 - Ind_Next_CP</t>
         </is>
@@ -16973,7 +17311,7 @@
           <t>260909FS24001458</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="I6" s="33" t="inlineStr">
         <is>
           <t>Deduction 1 of Top Picks - Ads - Ind_Next_Aug'26</t>
         </is>
@@ -17014,7 +17352,7 @@
           <t>260916FS24001471</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr">
+      <c r="I7" s="33" t="inlineStr">
         <is>
           <t>Deduction 2 of Ads Offers - Ads Growth Pack - Aug'26 - Ind_Next_CP</t>
         </is>
@@ -17055,7 +17393,7 @@
           <t>260916FS24001471</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t>Deduction 2 of Top Picks - Ads - Ind_Next_Aug'26</t>
         </is>
@@ -17096,7 +17434,7 @@
           <t>260923FS24003628</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr">
+      <c r="I9" s="33" t="inlineStr">
         <is>
           <t>Deduction 3 of Ads Offers - Ads Growth Pack - Aug'26 - Ind_Next_CP</t>
         </is>
@@ -17137,7 +17475,7 @@
           <t>260923FS24003628</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I10" s="33" t="inlineStr">
         <is>
           <t>Deduction 3 of Top Picks - Ads - Ind_Next_Aug'26</t>
         </is>
@@ -17178,7 +17516,7 @@
           <t>261001FS24001606</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I11" s="33" t="inlineStr">
         <is>
           <t>Deduction 4 of Ads Offers - Ads Growth Pack - Aug'26 - Ind_Next_CP</t>
         </is>
@@ -17219,7 +17557,7 @@
           <t>261001FS24001606</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="33" t="inlineStr">
         <is>
           <t>Deduction 4 of Top Picks - Ads - Ind_Next_Aug'26</t>
         </is>
@@ -17231,18 +17569,18 @@
           <t>27–30 Sep 2026</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="35" t="inlineStr">
         <is>
           <t>No ads investment / adjustment this cycle</t>
         </is>
       </c>
-      <c r="C13" s="37" t="n"/>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="37" t="n"/>
-      <c r="F13" s="37" t="n"/>
-      <c r="G13" s="37" t="n"/>
-      <c r="H13" s="37" t="n"/>
-      <c r="I13" s="37" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+      <c r="E13" s="36" t="n"/>
+      <c r="F13" s="36" t="n"/>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -17309,11 +17647,11 @@
           <t>Nil — no adjustment or refund recovered by Swiggy in any of the five cycles</t>
         </is>
       </c>
-      <c r="C18" s="37" t="n"/>
-      <c r="D18" s="37" t="n"/>
-      <c r="E18" s="37" t="n"/>
-      <c r="F18" s="37" t="n"/>
-      <c r="G18" s="37" t="n"/>
+      <c r="C18" s="36" t="n"/>
+      <c r="D18" s="36" t="n"/>
+      <c r="E18" s="36" t="n"/>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="36" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
@@ -17433,7 +17771,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="7" t="n"/>
-      <c r="H5" s="35" t="inlineStr">
+      <c r="H5" s="33" t="inlineStr">
         <is>
           <t>Unable to fetch Campaign Details</t>
         </is>
@@ -17463,7 +17801,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H6" s="33" t="inlineStr">
         <is>
           <t>Unable to fetch Campaign Details</t>
         </is>
@@ -17493,7 +17831,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="33" t="inlineStr">
         <is>
           <t>Unable to fetch Campaign Details</t>
         </is>
@@ -17523,7 +17861,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="H8" s="33" t="inlineStr">
         <is>
           <t>Unable to fetch Campaign Details</t>
         </is>
@@ -17553,7 +17891,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="35" t="inlineStr">
+      <c r="H9" s="33" t="inlineStr">
         <is>
           <t>Unable to fetch Campaign Details</t>
         </is>
@@ -17565,7 +17903,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E10" s="38" t="n">
+      <c r="E10" s="37" t="n">
         <v>75</v>
       </c>
     </row>

--- a/reports/Swiggy_Consolidated_Report.xlsx
+++ b/reports/Swiggy_Consolidated_Report.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -208,6 +208,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -901,7 +904,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>74 automated tie-out checks across every internal total and cross-sheet total, with exceptions flagged.</t>
+          <t>70+ automated tie-out checks across every internal total and cross-sheet total, with exceptions flagged.</t>
         </is>
       </c>
     </row>
@@ -1031,14 +1034,14 @@
       <c r="A5" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
       <c r="C5" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D5" s="31" t="n">
@@ -1050,7 +1053,7 @@
       <c r="F5" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="39" t="inlineStr">
+      <c r="G5" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1060,14 +1063,14 @@
       <c r="A6" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="39" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
       <c r="C6" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D6" s="32" t="n">
@@ -1079,7 +1082,7 @@
       <c r="F6" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="39" t="inlineStr">
+      <c r="G6" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1089,14 +1092,14 @@
       <c r="A7" s="31" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
       <c r="C7" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D7" s="32" t="n">
@@ -1108,7 +1111,7 @@
       <c r="F7" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="39" t="inlineStr">
+      <c r="G7" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1118,14 +1121,14 @@
       <c r="A8" s="31" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B8" s="39" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
       <c r="C8" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D8" s="32" t="n">
@@ -1137,7 +1140,7 @@
       <c r="F8" s="32" t="n">
         <v>-0</v>
       </c>
-      <c r="G8" s="39" t="inlineStr">
+      <c r="G8" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1147,14 +1150,14 @@
       <c r="A9" s="31" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
       <c r="C9" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D9" s="32" t="n">
@@ -1166,7 +1169,7 @@
       <c r="F9" s="32" t="n">
         <v>-0.02</v>
       </c>
-      <c r="G9" s="39" t="inlineStr">
+      <c r="G9" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1176,14 +1179,14 @@
       <c r="A10" s="31" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="38" t="inlineStr">
+      <c r="B10" s="39" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
       <c r="C10" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D10" s="32" t="n">
@@ -1195,7 +1198,7 @@
       <c r="F10" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G10" s="39" t="inlineStr">
+      <c r="G10" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1205,14 +1208,14 @@
       <c r="A11" s="31" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="38" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C11" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D11" s="32" t="n">
@@ -1224,7 +1227,7 @@
       <c r="F11" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="39" t="inlineStr">
+      <c r="G11" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1234,14 +1237,14 @@
       <c r="A12" s="31" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="38" t="inlineStr">
+      <c r="B12" s="39" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C12" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D12" s="31" t="n">
@@ -1253,7 +1256,7 @@
       <c r="F12" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="39" t="inlineStr">
+      <c r="G12" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1263,14 +1266,14 @@
       <c r="A13" s="31" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
       <c r="C13" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D13" s="32" t="n">
@@ -1282,7 +1285,7 @@
       <c r="F13" s="32" t="n">
         <v>0.05</v>
       </c>
-      <c r="G13" s="39" t="inlineStr">
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1292,14 +1295,14 @@
       <c r="A14" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="39" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
@@ -1311,7 +1314,7 @@
       <c r="F14" s="32" t="n">
         <v>-0.11</v>
       </c>
-      <c r="G14" s="39" t="inlineStr">
+      <c r="G14" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1321,14 +1324,14 @@
       <c r="A15" s="31" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
       <c r="C15" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D15" s="32" t="n">
@@ -1340,7 +1343,7 @@
       <c r="F15" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G15" s="39" t="inlineStr">
+      <c r="G15" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1350,14 +1353,14 @@
       <c r="A16" s="31" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="38" t="inlineStr">
+      <c r="B16" s="39" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
       <c r="C16" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D16" s="32" t="n">
@@ -1369,7 +1372,7 @@
       <c r="F16" s="32" t="n">
         <v>5.95</v>
       </c>
-      <c r="G16" s="40" t="inlineStr">
+      <c r="G16" s="41" t="inlineStr">
         <is>
           <t>EXPLAINED</t>
         </is>
@@ -1379,14 +1382,14 @@
       <c r="A17" s="31" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
       <c r="C17" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D17" s="32" t="n">
@@ -1398,7 +1401,7 @@
       <c r="F17" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="39" t="inlineStr">
+      <c r="G17" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1408,14 +1411,14 @@
       <c r="A18" s="31" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="38" t="inlineStr">
+      <c r="B18" s="39" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
       <c r="C18" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D18" s="31" t="n">
@@ -1427,7 +1430,7 @@
       <c r="F18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="39" t="inlineStr">
+      <c r="G18" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1437,14 +1440,14 @@
       <c r="A19" s="31" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
       <c r="C19" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D19" s="32" t="n">
@@ -1456,7 +1459,7 @@
       <c r="F19" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G19" s="39" t="inlineStr">
+      <c r="G19" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1466,14 +1469,14 @@
       <c r="A20" s="31" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="38" t="inlineStr">
+      <c r="B20" s="39" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
       <c r="C20" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D20" s="32" t="n">
@@ -1485,7 +1488,7 @@
       <c r="F20" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G20" s="39" t="inlineStr">
+      <c r="G20" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1495,14 +1498,14 @@
       <c r="A21" s="31" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="39" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
       <c r="C21" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D21" s="32" t="n">
@@ -1514,7 +1517,7 @@
       <c r="F21" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G21" s="39" t="inlineStr">
+      <c r="G21" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1524,14 +1527,14 @@
       <c r="A22" s="31" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="38" t="inlineStr">
+      <c r="B22" s="39" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
       <c r="C22" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D22" s="32" t="n">
@@ -1543,7 +1546,7 @@
       <c r="F22" s="32" t="n">
         <v>0.04</v>
       </c>
-      <c r="G22" s="39" t="inlineStr">
+      <c r="G22" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1553,14 +1556,14 @@
       <c r="A23" s="31" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="38" t="inlineStr">
+      <c r="B23" s="39" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
       <c r="C23" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D23" s="32" t="n">
@@ -1572,7 +1575,7 @@
       <c r="F23" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="39" t="inlineStr">
+      <c r="G23" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1582,14 +1585,14 @@
       <c r="A24" s="31" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="38" t="inlineStr">
+      <c r="B24" s="39" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D24" s="32" t="n">
@@ -1601,7 +1604,7 @@
       <c r="F24" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G24" s="39" t="inlineStr">
+      <c r="G24" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1611,14 +1614,14 @@
       <c r="A25" s="31" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="38" t="inlineStr">
+      <c r="B25" s="39" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C25" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D25" s="31" t="n">
@@ -1630,7 +1633,7 @@
       <c r="F25" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="39" t="inlineStr">
+      <c r="G25" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1640,14 +1643,14 @@
       <c r="A26" s="31" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="38" t="inlineStr">
+      <c r="B26" s="39" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
       <c r="C26" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D26" s="32" t="n">
@@ -1659,7 +1662,7 @@
       <c r="F26" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G26" s="39" t="inlineStr">
+      <c r="G26" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1669,14 +1672,14 @@
       <c r="A27" s="31" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="38" t="inlineStr">
+      <c r="B27" s="39" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
       <c r="C27" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D27" s="32" t="n">
@@ -1688,7 +1691,7 @@
       <c r="F27" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G27" s="39" t="inlineStr">
+      <c r="G27" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1698,14 +1701,14 @@
       <c r="A28" s="31" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="38" t="inlineStr">
+      <c r="B28" s="39" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
       <c r="C28" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D28" s="32" t="n">
@@ -1717,7 +1720,7 @@
       <c r="F28" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G28" s="39" t="inlineStr">
+      <c r="G28" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1727,14 +1730,14 @@
       <c r="A29" s="31" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="39" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
       <c r="C29" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D29" s="32" t="n">
@@ -1746,7 +1749,7 @@
       <c r="F29" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G29" s="40" t="inlineStr">
+      <c r="G29" s="41" t="inlineStr">
         <is>
           <t>EXPLAINED</t>
         </is>
@@ -1756,14 +1759,14 @@
       <c r="A30" s="31" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="38" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
       <c r="C30" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="D30" s="32" t="n">
@@ -1775,7 +1778,7 @@
       <c r="F30" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G30" s="39" t="inlineStr">
+      <c r="G30" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1785,14 +1788,14 @@
       <c r="A31" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="38" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
       <c r="C31" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D31" s="31" t="n">
@@ -1804,7 +1807,7 @@
       <c r="F31" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G31" s="39" t="inlineStr">
+      <c r="G31" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1814,14 +1817,14 @@
       <c r="A32" s="31" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="38" t="inlineStr">
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
       <c r="C32" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D32" s="32" t="n">
@@ -1833,7 +1836,7 @@
       <c r="F32" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G32" s="39" t="inlineStr">
+      <c r="G32" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1843,14 +1846,14 @@
       <c r="A33" s="31" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="38" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
       <c r="C33" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D33" s="32" t="n">
@@ -1862,7 +1865,7 @@
       <c r="F33" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G33" s="39" t="inlineStr">
+      <c r="G33" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1872,14 +1875,14 @@
       <c r="A34" s="31" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="38" t="inlineStr">
+      <c r="B34" s="39" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
       <c r="C34" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D34" s="32" t="n">
@@ -1891,7 +1894,7 @@
       <c r="F34" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="39" t="inlineStr">
+      <c r="G34" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1901,14 +1904,14 @@
       <c r="A35" s="31" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B35" s="39" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
       <c r="C35" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D35" s="32" t="n">
@@ -1920,7 +1923,7 @@
       <c r="F35" s="32" t="n">
         <v>-0.17</v>
       </c>
-      <c r="G35" s="39" t="inlineStr">
+      <c r="G35" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1930,14 +1933,14 @@
       <c r="A36" s="31" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="38" t="inlineStr">
+      <c r="B36" s="39" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
       <c r="C36" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D36" s="32" t="n">
@@ -1949,7 +1952,7 @@
       <c r="F36" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G36" s="39" t="inlineStr">
+      <c r="G36" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1959,14 +1962,14 @@
       <c r="A37" s="31" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="39" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C37" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D37" s="32" t="n">
@@ -1978,7 +1981,7 @@
       <c r="F37" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="39" t="inlineStr">
+      <c r="G37" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1988,14 +1991,14 @@
       <c r="A38" s="31" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="38" t="inlineStr">
+      <c r="B38" s="39" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C38" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D38" s="31" t="n">
@@ -2007,7 +2010,7 @@
       <c r="F38" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G38" s="39" t="inlineStr">
+      <c r="G38" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2017,14 +2020,14 @@
       <c r="A39" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="38" t="inlineStr">
+      <c r="B39" s="39" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
       <c r="C39" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D39" s="32" t="n">
@@ -2036,7 +2039,7 @@
       <c r="F39" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G39" s="39" t="inlineStr">
+      <c r="G39" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2046,14 +2049,14 @@
       <c r="A40" s="31" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="38" t="inlineStr">
+      <c r="B40" s="39" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
       <c r="C40" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D40" s="32" t="n">
@@ -2065,7 +2068,7 @@
       <c r="F40" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="39" t="inlineStr">
+      <c r="G40" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2075,14 +2078,14 @@
       <c r="A41" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="38" t="inlineStr">
+      <c r="B41" s="39" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
       <c r="C41" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D41" s="32" t="n">
@@ -2094,7 +2097,7 @@
       <c r="F41" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="39" t="inlineStr">
+      <c r="G41" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2104,14 +2107,14 @@
       <c r="A42" s="31" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="38" t="inlineStr">
+      <c r="B42" s="39" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
       <c r="C42" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D42" s="32" t="n">
@@ -2123,7 +2126,7 @@
       <c r="F42" s="32" t="n">
         <v>0.03</v>
       </c>
-      <c r="G42" s="40" t="inlineStr">
+      <c r="G42" s="41" t="inlineStr">
         <is>
           <t>EXPLAINED</t>
         </is>
@@ -2133,14 +2136,14 @@
       <c r="A43" s="31" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="38" t="inlineStr">
+      <c r="B43" s="39" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
       <c r="C43" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="D43" s="32" t="n">
@@ -2152,7 +2155,7 @@
       <c r="F43" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="39" t="inlineStr">
+      <c r="G43" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2162,14 +2165,14 @@
       <c r="A44" s="31" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="38" t="inlineStr">
+      <c r="B44" s="39" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
       <c r="C44" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D44" s="31" t="n">
@@ -2181,7 +2184,7 @@
       <c r="F44" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="39" t="inlineStr">
+      <c r="G44" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2191,14 +2194,14 @@
       <c r="A45" s="31" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="38" t="inlineStr">
+      <c r="B45" s="39" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D45" s="32" t="n">
@@ -2210,7 +2213,7 @@
       <c r="F45" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G45" s="39" t="inlineStr">
+      <c r="G45" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2220,14 +2223,14 @@
       <c r="A46" s="31" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="38" t="inlineStr">
+      <c r="B46" s="39" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D46" s="32" t="n">
@@ -2239,7 +2242,7 @@
       <c r="F46" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G46" s="39" t="inlineStr">
+      <c r="G46" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2249,14 +2252,14 @@
       <c r="A47" s="31" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="38" t="inlineStr">
+      <c r="B47" s="39" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D47" s="32" t="n">
@@ -2268,7 +2271,7 @@
       <c r="F47" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G47" s="39" t="inlineStr">
+      <c r="G47" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2278,14 +2281,14 @@
       <c r="A48" s="31" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="38" t="inlineStr">
+      <c r="B48" s="39" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D48" s="32" t="n">
@@ -2297,7 +2300,7 @@
       <c r="F48" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G48" s="39" t="inlineStr">
+      <c r="G48" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2307,14 +2310,14 @@
       <c r="A49" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="38" t="inlineStr">
+      <c r="B49" s="39" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D49" s="32" t="n">
@@ -2326,7 +2329,7 @@
       <c r="F49" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G49" s="39" t="inlineStr">
+      <c r="G49" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2336,14 +2339,14 @@
       <c r="A50" s="31" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="38" t="inlineStr">
+      <c r="B50" s="39" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D50" s="32" t="n">
@@ -2355,7 +2358,7 @@
       <c r="F50" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G50" s="39" t="inlineStr">
+      <c r="G50" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2365,14 +2368,14 @@
       <c r="A51" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="38" t="inlineStr">
+      <c r="B51" s="39" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D51" s="31" t="n">
@@ -2384,7 +2387,7 @@
       <c r="F51" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G51" s="39" t="inlineStr">
+      <c r="G51" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2394,14 +2397,14 @@
       <c r="A52" s="31" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="38" t="inlineStr">
+      <c r="B52" s="39" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
       <c r="C52" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D52" s="32" t="n">
@@ -2413,7 +2416,7 @@
       <c r="F52" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G52" s="39" t="inlineStr">
+      <c r="G52" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2423,14 +2426,14 @@
       <c r="A53" s="31" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="38" t="inlineStr">
+      <c r="B53" s="39" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D53" s="32" t="n">
@@ -2442,7 +2445,7 @@
       <c r="F53" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G53" s="39" t="inlineStr">
+      <c r="G53" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2452,14 +2455,14 @@
       <c r="A54" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="38" t="inlineStr">
+      <c r="B54" s="39" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
       <c r="C54" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D54" s="32" t="n">
@@ -2471,7 +2474,7 @@
       <c r="F54" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G54" s="39" t="inlineStr">
+      <c r="G54" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2481,14 +2484,14 @@
       <c r="A55" s="31" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="38" t="inlineStr">
+      <c r="B55" s="39" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D55" s="32" t="n">
@@ -2500,7 +2503,7 @@
       <c r="F55" s="32" t="n">
         <v>0.01</v>
       </c>
-      <c r="G55" s="39" t="inlineStr">
+      <c r="G55" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2510,14 +2513,14 @@
       <c r="A56" s="31" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="38" t="inlineStr">
+      <c r="B56" s="39" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="D56" s="32" t="n">
@@ -2529,7 +2532,7 @@
       <c r="F56" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G56" s="39" t="inlineStr">
+      <c r="G56" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2539,14 +2542,14 @@
       <c r="A57" s="31" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="38" t="inlineStr">
+      <c r="B57" s="39" t="inlineStr">
         <is>
           <t>Order-level rows = orders in payout breakup = stated total orders</t>
         </is>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D57" s="31" t="n">
@@ -2558,7 +2561,7 @@
       <c r="F57" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G57" s="39" t="inlineStr">
+      <c r="G57" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2568,14 +2571,14 @@
       <c r="A58" s="31" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="38" t="inlineStr">
+      <c r="B58" s="39" t="inlineStr">
         <is>
           <t>Total customer paid (order level) = payout breakup line A</t>
         </is>
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D58" s="32" t="n">
@@ -2587,7 +2590,7 @@
       <c r="F58" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G58" s="39" t="inlineStr">
+      <c r="G58" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2597,14 +2600,14 @@
       <c r="A59" s="31" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="38" t="inlineStr">
+      <c r="B59" s="39" t="inlineStr">
         <is>
           <t>GST collected (order level) = payout breakup line 5</t>
         </is>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D59" s="32" t="n">
@@ -2616,7 +2619,7 @@
       <c r="F59" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="39" t="inlineStr">
+      <c r="G59" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2626,14 +2629,14 @@
       <c r="A60" s="31" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="38" t="inlineStr">
+      <c r="B60" s="39" t="inlineStr">
         <is>
           <t>Net payout (order level) = payout breakup G delivered + cancelled</t>
         </is>
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D60" s="32" t="n">
@@ -2645,7 +2648,7 @@
       <c r="F60" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G60" s="39" t="inlineStr">
+      <c r="G60" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2655,14 +2658,14 @@
       <c r="A61" s="31" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="38" t="inlineStr">
+      <c r="B61" s="39" t="inlineStr">
         <is>
           <t>Payout equation A+B+C+D+E+F = G (net payout)</t>
         </is>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D61" s="32" t="n">
@@ -2674,7 +2677,7 @@
       <c r="F61" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G61" s="39" t="inlineStr">
+      <c r="G61" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2684,14 +2687,14 @@
       <c r="A62" s="31" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="38" t="inlineStr">
+      <c r="B62" s="39" t="inlineStr">
         <is>
           <t>Delivered + cancelled + ads = total net payout</t>
         </is>
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D62" s="32" t="n">
@@ -2703,7 +2706,7 @@
       <c r="F62" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G62" s="39" t="inlineStr">
+      <c r="G62" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2713,14 +2716,14 @@
       <c r="A63" s="31" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="38" t="inlineStr">
+      <c r="B63" s="39" t="inlineStr">
         <is>
           <t>Net payout = 'Total Payout' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D63" s="32" t="n">
@@ -2732,7 +2735,7 @@
       <c r="F63" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G63" s="39" t="inlineStr">
+      <c r="G63" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2742,14 +2745,14 @@
       <c r="A64" s="31" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="38" t="inlineStr">
+      <c r="B64" s="39" t="inlineStr">
         <is>
           <t>Order rows = 'Total Orders' printed on the Summary sheet</t>
         </is>
       </c>
       <c r="C64" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D64" s="31" t="n">
@@ -2761,7 +2764,7 @@
       <c r="F64" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G64" s="39" t="inlineStr">
+      <c r="G64" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2771,14 +2774,14 @@
       <c r="A65" s="31" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="38" t="inlineStr">
+      <c r="B65" s="39" t="inlineStr">
         <is>
           <t>GST collected = 5% of the billed value (memo, before the cancellation adjustment)</t>
         </is>
       </c>
       <c r="C65" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D65" s="32" t="n">
@@ -2790,7 +2793,7 @@
       <c r="F65" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G65" s="39" t="inlineStr">
+      <c r="G65" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2800,14 +2803,14 @@
       <c r="A66" s="31" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="38" t="inlineStr">
+      <c r="B66" s="39" t="inlineStr">
         <is>
           <t>TDS u/s 194-O vs 0.1% of item total</t>
         </is>
       </c>
       <c r="C66" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D66" s="32" t="n">
@@ -2819,7 +2822,7 @@
       <c r="F66" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G66" s="39" t="inlineStr">
+      <c r="G66" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2829,14 +2832,14 @@
       <c r="A67" s="31" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="38" t="inlineStr">
+      <c r="B67" s="39" t="inlineStr">
         <is>
           <t>GST discharged by Swiggy = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
       <c r="C67" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D67" s="32" t="n">
@@ -2848,7 +2851,7 @@
       <c r="F67" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G67" s="39" t="inlineStr">
+      <c r="G67" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2858,14 +2861,14 @@
       <c r="A68" s="31" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="38" t="inlineStr">
+      <c r="B68" s="39" t="inlineStr">
         <is>
           <t>GST collected from customers vs GST discharged by Swiggy — explained</t>
         </is>
       </c>
       <c r="C68" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D68" s="32" t="n">
@@ -2877,7 +2880,7 @@
       <c r="F68" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="39" t="inlineStr">
+      <c r="G68" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2887,14 +2890,14 @@
       <c r="A69" s="31" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="38" t="inlineStr">
+      <c r="B69" s="39" t="inlineStr">
         <is>
           <t>TCS u/s 52 deducted</t>
         </is>
       </c>
       <c r="C69" s="31" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="D69" s="32" t="n">
@@ -2906,7 +2909,7 @@
       <c r="F69" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="39" t="inlineStr">
+      <c r="G69" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2916,14 +2919,14 @@
       <c r="A70" s="31" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="38" t="inlineStr">
+      <c r="B70" s="39" t="inlineStr">
         <is>
           <t>Compensation + un-compensated deduction = amount paid by the customer</t>
         </is>
       </c>
       <c r="C70" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026 · 247576408124202</t>
+          <t>01 – 05 Sep · 247576408124202</t>
         </is>
       </c>
       <c r="D70" s="32" t="n">
@@ -2935,7 +2938,7 @@
       <c r="F70" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G70" s="39" t="inlineStr">
+      <c r="G70" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2945,14 +2948,14 @@
       <c r="A71" s="31" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="38" t="inlineStr">
+      <c r="B71" s="39" t="inlineStr">
         <is>
           <t>Compensation + un-compensated value = net bill value</t>
         </is>
       </c>
       <c r="C71" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026 · 247576408124202</t>
+          <t>01 – 05 Sep · 247576408124202</t>
         </is>
       </c>
       <c r="D71" s="32" t="n">
@@ -2964,7 +2967,7 @@
       <c r="F71" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G71" s="39" t="inlineStr">
+      <c r="G71" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2974,14 +2977,14 @@
       <c r="A72" s="31" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="38" t="inlineStr">
-        <is>
-          <t>Complaint &amp; cancellation charges = 20% of net bill value + 5% GST (₹118.00 × 1.05)</t>
+      <c r="B72" s="39" t="inlineStr">
+        <is>
+          <t>Complaint &amp; cancellation charges = un-compensated 20% + 5% GST (₹118.00 × 1.05)</t>
         </is>
       </c>
       <c r="C72" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026 · 247576408124202</t>
+          <t>01 – 05 Sep · 247576408124202</t>
         </is>
       </c>
       <c r="D72" s="32" t="n">
@@ -2993,7 +2996,7 @@
       <c r="F72" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G72" s="39" t="inlineStr">
+      <c r="G72" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3003,14 +3006,14 @@
       <c r="A73" s="31" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="38" t="inlineStr">
+      <c r="B73" s="39" t="inlineStr">
         <is>
           <t>GST collected = GST discharged + GST on the un-compensated 20%</t>
         </is>
       </c>
       <c r="C73" s="31" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026 · 247576408124202</t>
+          <t>01 – 05 Sep · 247576408124202</t>
         </is>
       </c>
       <c r="D73" s="32" t="n">
@@ -3022,7 +3025,7 @@
       <c r="F73" s="32" t="n">
         <v>-0</v>
       </c>
-      <c r="G73" s="39" t="inlineStr">
+      <c r="G73" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3032,14 +3035,14 @@
       <c r="A74" s="31" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="38" t="inlineStr">
+      <c r="B74" s="39" t="inlineStr">
         <is>
           <t>Restaurant-cancelled order: no supply, no GST discharged on the food</t>
         </is>
       </c>
       <c r="C74" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026 · 248201907107833</t>
+          <t>06 – 12 Sep · 248201907107833</t>
         </is>
       </c>
       <c r="D74" s="32" t="n">
@@ -3051,7 +3054,7 @@
       <c r="F74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G74" s="39" t="inlineStr">
+      <c r="G74" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3061,14 +3064,14 @@
       <c r="A75" s="31" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="38" t="inlineStr">
+      <c r="B75" s="39" t="inlineStr">
         <is>
           <t>Restaurant-cancelled order: no supply, no GST discharged on the food</t>
         </is>
       </c>
       <c r="C75" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026 · 248773805195420</t>
+          <t>13 – 19 Sep · 248773805195420</t>
         </is>
       </c>
       <c r="D75" s="32" t="n">
@@ -3080,7 +3083,7 @@
       <c r="F75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="39" t="inlineStr">
+      <c r="G75" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3090,14 +3093,14 @@
       <c r="A76" s="31" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="38" t="inlineStr">
+      <c r="B76" s="39" t="inlineStr">
         <is>
           <t>Month: complaint &amp; cancellation charges (payout line C) = un-compensated 20% + 5% GST</t>
         </is>
       </c>
       <c r="C76" s="31" t="inlineStr">
         <is>
-          <t>All cycles</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D76" s="32" t="n">
@@ -3109,7 +3112,7 @@
       <c r="F76" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G76" s="39" t="inlineStr">
+      <c r="G76" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3119,14 +3122,14 @@
       <c r="A77" s="31" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="38" t="inlineStr">
+      <c r="B77" s="39" t="inlineStr">
         <is>
           <t>Month: GST discharged = 5% of compensation-adjusted reportable value</t>
         </is>
       </c>
       <c r="C77" s="31" t="inlineStr">
         <is>
-          <t>All cycles</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D77" s="32" t="n">
@@ -3138,7 +3141,7 @@
       <c r="F77" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="39" t="inlineStr">
+      <c r="G77" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3148,14 +3151,14 @@
       <c r="A78" s="31" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="38" t="inlineStr">
+      <c r="B78" s="39" t="inlineStr">
         <is>
           <t>Month: residual GST difference after the cancellation policy (pure paise rounding)</t>
         </is>
       </c>
       <c r="C78" s="31" t="inlineStr">
         <is>
-          <t>All cycles</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D78" s="32" t="n">
@@ -3167,7 +3170,7 @@
       <c r="F78" s="32" t="n">
         <v>0.12</v>
       </c>
-      <c r="G78" s="39" t="inlineStr">
+      <c r="G78" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3177,7 +3180,7 @@
       <c r="A79" s="31" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="38" t="inlineStr">
+      <c r="B79" s="39" t="inlineStr">
         <is>
           <t>Order-wise net payout = customer paid − Swiggy fees − complaint/cancellation − taxes</t>
         </is>
@@ -3200,7 +3203,7 @@
       <c r="F79" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="G79" s="39" t="inlineStr">
+      <c r="G79" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3210,7 +3213,7 @@
       <c r="A80" s="31" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="38" t="inlineStr">
+      <c r="B80" s="39" t="inlineStr">
         <is>
           <t>Highest paise-level rounding inside the annexures (tolerated, not adjusted)</t>
         </is>
@@ -3231,7 +3234,7 @@
         </is>
       </c>
       <c r="F80" s="31" t="n"/>
-      <c r="G80" s="39" t="inlineStr">
+      <c r="G80" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3241,7 +3244,7 @@
       <c r="A81" s="31" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="38" t="inlineStr">
+      <c r="B81" s="39" t="inlineStr">
         <is>
           <t>Duplicate Order IDs across payout cycles</t>
         </is>
@@ -3262,7 +3265,7 @@
       <c r="F81" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G81" s="39" t="inlineStr">
+      <c r="G81" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3272,14 +3275,14 @@
       <c r="A82" s="31" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="38" t="inlineStr">
+      <c r="B82" s="39" t="inlineStr">
         <is>
           <t>Payout cycles are continuous with no gap/overlap</t>
         </is>
       </c>
       <c r="C82" s="31" t="inlineStr">
         <is>
-          <t>01–30 Sep 2026</t>
+          <t>01 Sep – 30 Sep 2026</t>
         </is>
       </c>
       <c r="D82" s="31" t="inlineStr">
@@ -3295,7 +3298,7 @@
       <c r="F82" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="39" t="inlineStr">
+      <c r="G82" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3305,14 +3308,14 @@
       <c r="A83" s="31" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="38" t="inlineStr">
-        <is>
-          <t>Coverage of the month</t>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t>Coverage of the period</t>
         </is>
       </c>
       <c r="C83" s="31" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D83" s="31" t="inlineStr">
@@ -3326,7 +3329,7 @@
         </is>
       </c>
       <c r="F83" s="31" t="n"/>
-      <c r="G83" s="39" t="inlineStr">
+      <c r="G83" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3336,14 +3339,14 @@
       <c r="A84" s="31" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="38" t="inlineStr">
-        <is>
-          <t>Coverage of the month — end</t>
+      <c r="B84" s="39" t="inlineStr">
+        <is>
+          <t>Coverage of the period — end</t>
         </is>
       </c>
       <c r="C84" s="31" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>September 2026</t>
         </is>
       </c>
       <c r="D84" s="31" t="inlineStr">
@@ -3357,7 +3360,7 @@
         </is>
       </c>
       <c r="F84" s="31" t="n"/>
-      <c r="G84" s="39" t="inlineStr">
+      <c r="G84" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3367,7 +3370,7 @@
       <c r="A85" s="31" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="38" t="inlineStr">
+      <c r="B85" s="39" t="inlineStr">
         <is>
           <t>Unresolved customer complaints outstanding</t>
         </is>
@@ -3386,7 +3389,7 @@
       <c r="F85" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="G85" s="39" t="inlineStr">
+      <c r="G85" s="40" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3401,35 +3404,35 @@
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
-      <c r="B88" s="41" t="inlineStr">
-        <is>
-          <t>•  GST discharged by Swiggy (₹2,305.92) is ₹6.02 lower than the GST billed to customers (₹2,311.94). This is CORRECT and not a discrepancy: ₹5.90 of it is the effect of the cancellation-compensation policy (order 247576408124202 in the 01–05 Sep cycle was cancelled before pickup and is compensated at 80% of the order value, so GST was discharged on ₹472.00 instead of ₹590.00), and the remaining ₹0.12 is paise rounding on the other orders. See the 'Cancelled Orders' sheet and the GST working workbook → Sec 9(5) Reconciliation.</t>
+      <c r="B88" s="42" t="inlineStr">
+        <is>
+          <t>•  GST discharged by Swiggy (₹2,305.92) is ₹6.02 lower than the GST billed to customers (₹2,311.94). This is CORRECT and not a discrepancy: ₹5.90 of it is the effect of the cancellation-compensation policy (order 247576408124202 in the 01 – 05 Sep cycle was cancelled before pickup and is compensated at 80% of the order value, so GST was discharged on ₹472.00 instead of ₹590.00), and the remaining ₹0.12 is paise rounding on the other orders. See the 'Cancelled Orders' sheet and the GST working workbook → Sec 9(5) Reconciliation.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
-      <c r="B89" s="41" t="inlineStr">
+      <c r="B89" s="42" t="inlineStr">
         <is>
           <t>•  The 20–26 Sep cycle's annexure is generated on 01 Oct and the 27–30 Sep cycle is a four-day cycle — payout cycles are not equal length, so compare rates (not totals) across cycles.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
-      <c r="B90" s="41" t="inlineStr">
+      <c r="B90" s="42" t="inlineStr">
         <is>
           <t>•  Ads investments of ₹680.84 were recovered in 4 of the 5 cycles against 'Aug-26' ad packs (₹170.21 per cycle: Top Picks ₹110.62 + Ads Offers ₹59.59), and nil in the 27–30 Sep cycle.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
-      <c r="B91" s="41" t="inlineStr">
-        <is>
-          <t>•  The Discount Summary sheet in every annexure says 'Unable to fetch Campaign Details' — Swiggy has not given the coupon-level discount breakdown even though 8–21 orders per cycle carried a discount code (75 orders across the month).</t>
+      <c r="B91" s="42" t="inlineStr">
+        <is>
+          <t>•  The Discount Summary sheet says 'Unable to fetch Campaign Details' — Swiggy has not given the coupon-level discount breakdown even though 8-21 orders per cycle carried a discount code (75 orders in total).</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
-      <c r="B92" s="41" t="inlineStr">
+      <c r="B92" s="42" t="inlineStr">
         <is>
           <t>•  Differences of a few paise on the payout equations are Swiggy's own rounding inside the annexures (the same cycle shows a paise difference between its delivered/cancelled columns and its total column); they are disclosed here rather than adjusted.</t>
         </is>
@@ -3912,21 +3915,21 @@
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="41" t="inlineStr">
+      <c r="A34" s="42" t="inlineStr">
         <is>
           <t>•  In the Order Level sheet, 'Total Swiggy Fees' is inclusive of the 18% GST charged on Swiggy's own service fee.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="41" t="inlineStr">
+      <c r="A35" s="42" t="inlineStr">
         <is>
           <t>•  In the Payout Breakup, 'Swiggy Fees' (line B) excludes that GST — it appears separately as line 19 'GST on Service Fee @18%'. The payout equation A+B+C+D+E+F=G therefore ties only with the payout-breakup convention.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="41" t="inlineStr">
+      <c r="A36" s="42" t="inlineStr">
         <is>
           <t>•  'GST Deduction' (line 18) is the 5% GST on the food supply that Swiggy retains and deposits under Section 9(5) of the CGST Act — it is not a charge on the restaurant.</t>
         </is>
@@ -4097,7 +4100,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B2" s="8" t="n">
@@ -4173,7 +4176,7 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B3" s="12" t="n">
@@ -4249,7 +4252,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
@@ -4325,7 +4328,7 @@
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
@@ -4401,7 +4404,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -4541,7 +4544,7 @@
     <row r="9">
       <c r="A9" s="18" t="inlineStr">
         <is>
-          <t>Totals = the five weekly annexures for 01 Sep 2026 – 30 Sep 2026. Settlement dates are as printed on each annexure. Deduction lines (commission, charges, ads, GST, TDS) are shown here as positive amounts for readability — the annexures print them as negative; see the Payout Breakup sheet for the original signs.</t>
+          <t>Totals = the five annexure(s) covering 01 Sep – 30 Sep 2026. Settlement dates are as printed on each annexure. Deduction lines (commission, charges, ads, GST, TDS) are shown here as positive amounts for readability — the annexures print them as negative; see the Payout Breakup sheet for the original signs.</t>
         </is>
       </c>
     </row>
@@ -4583,27 +4586,27 @@
       </c>
       <c r="C1" s="6" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="H1" s="6" t="inlineStr">
@@ -5546,7 +5549,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
@@ -5592,7 +5595,7 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
@@ -5638,7 +5641,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
@@ -5684,7 +5687,7 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -5730,7 +5733,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
@@ -6039,7 +6042,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B2" s="7" t="inlineStr">
@@ -6149,7 +6152,7 @@
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
@@ -6259,7 +6262,7 @@
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -6369,7 +6372,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -6479,7 +6482,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -6589,7 +6592,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -6699,7 +6702,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -6813,7 +6816,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -6919,7 +6922,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -7029,7 +7032,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -7143,7 +7146,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -7253,7 +7256,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -7363,7 +7366,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -7473,7 +7476,7 @@
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B15" s="24" t="inlineStr">
@@ -7583,7 +7586,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
@@ -7689,7 +7692,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -7799,7 +7802,7 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
@@ -7905,7 +7908,7 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -8011,7 +8014,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
@@ -8117,7 +8120,7 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
@@ -8227,7 +8230,7 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B22" s="11" t="inlineStr">
@@ -8337,7 +8340,7 @@
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
@@ -8451,7 +8454,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B24" s="11" t="inlineStr">
@@ -8561,7 +8564,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
@@ -8667,7 +8670,7 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B26" s="11" t="inlineStr">
@@ -8781,7 +8784,7 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
@@ -8891,7 +8894,7 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B28" s="11" t="inlineStr">
@@ -9001,7 +9004,7 @@
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
@@ -9111,7 +9114,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
@@ -9221,7 +9224,7 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
@@ -9335,7 +9338,7 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
@@ -9445,7 +9448,7 @@
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
@@ -9551,7 +9554,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B34" s="11" t="inlineStr">
@@ -9661,7 +9664,7 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
@@ -9771,7 +9774,7 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B36" s="11" t="inlineStr">
@@ -9881,7 +9884,7 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
@@ -9991,7 +9994,7 @@
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B38" s="11" t="inlineStr">
@@ -10101,7 +10104,7 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
@@ -10211,7 +10214,7 @@
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B40" s="11" t="inlineStr">
@@ -10317,7 +10320,7 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
@@ -10427,7 +10430,7 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B42" s="11" t="inlineStr">
@@ -10541,7 +10544,7 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
@@ -10651,7 +10654,7 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B44" s="11" t="inlineStr">
@@ -10761,7 +10764,7 @@
     <row r="45">
       <c r="A45" s="24" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B45" s="24" t="inlineStr">
@@ -10871,7 +10874,7 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -10981,7 +10984,7 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -11091,7 +11094,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -11201,7 +11204,7 @@
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
@@ -11315,7 +11318,7 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -11425,7 +11428,7 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
@@ -11539,7 +11542,7 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -11649,7 +11652,7 @@
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -11763,7 +11766,7 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -11873,7 +11876,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -11983,7 +11986,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -12093,7 +12096,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -12207,7 +12210,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -12313,7 +12316,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -12423,7 +12426,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -12533,7 +12536,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -12643,7 +12646,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -12753,7 +12756,7 @@
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -12859,7 +12862,7 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -12969,7 +12972,7 @@
     <row r="65">
       <c r="A65" s="24" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B65" s="24" t="inlineStr">
@@ -13087,7 +13090,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -13197,7 +13200,7 @@
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -13311,7 +13314,7 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
@@ -13425,7 +13428,7 @@
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
@@ -13531,7 +13534,7 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -13641,7 +13644,7 @@
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -13751,7 +13754,7 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
@@ -13857,7 +13860,7 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
@@ -13967,7 +13970,7 @@
     <row r="74">
       <c r="A74" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B74" s="11" t="inlineStr">
@@ -14077,7 +14080,7 @@
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
@@ -14187,7 +14190,7 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B76" s="11" t="inlineStr">
@@ -14297,7 +14300,7 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
@@ -14411,7 +14414,7 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B78" s="11" t="inlineStr">
@@ -14521,7 +14524,7 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
@@ -14631,7 +14634,7 @@
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
@@ -14741,7 +14744,7 @@
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
@@ -14851,7 +14854,7 @@
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -14961,7 +14964,7 @@
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -15075,7 +15078,7 @@
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -15181,7 +15184,7 @@
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -15291,7 +15294,7 @@
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -15401,7 +15404,7 @@
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -15511,7 +15514,7 @@
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -15625,7 +15628,7 @@
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -15731,7 +15734,7 @@
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
@@ -15841,7 +15844,7 @@
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -15951,7 +15954,7 @@
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
@@ -16061,7 +16064,7 @@
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
@@ -16171,7 +16174,7 @@
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
@@ -16281,7 +16284,7 @@
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
@@ -16391,7 +16394,7 @@
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
@@ -16497,7 +16500,7 @@
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>Every order row from all 5 annexures (95.0 orders). Cancelled-order rows are shaded amber. 'Taxable value' = item total + packaging − restaurant-funded discounts (the full value billed to the customer). 'GST-reportable value' is the same figure, except that an order cancelled before pickup by the customer/Swiggy is reported at the 80% compensation value — see the 'Cancelled Orders' sheet.</t>
+          <t>Every order row from all 5 annexure(s) (95 orders). Cancelled-order rows are shaded amber. 'Taxable value' = item total + packaging − restaurant-funded discounts (the full value billed to the customer). 'GST-reportable value' is the same figure, except that an order cancelled before pickup by the customer/Swiggy is reported at the 80% compensation value — see the 'Cancelled Orders' sheet.</t>
         </is>
       </c>
     </row>
@@ -16559,14 +16562,14 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>The restaurant is taxed on the 80% compensation, not on the full value the customer had paid, and the un-compensated 20%</t>
+          <t>The restaurant is taxed on the 80% compensation, not on the full value the customer had paid, and the un-compensated 20% is deducted from the payout as a GST-inclusive amount.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>is deducted from the payout as a GST-inclusive amount. For order 247576408124202 (net bill value ₹590.00):</t>
+          <t>For order 247576408124202 (net bill value ₹590.00), in the 01 – 05 Sep cycle — cancelled by Swiggy:</t>
         </is>
       </c>
     </row>
@@ -16580,7 +16583,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">        un-compensated 20% × 590.00 = 118.00  + GST 5%  5.90  =  123.90  → 'Complaint &amp; Cancellation Charges [18+19]'</t>
+          <t xml:space="preserve">        un-compensated 20% × 590.00 = 118.00  + GST 5% 5.90  =  123.90  → 'Complaint &amp; Cancellation Charges [18+19]'</t>
         </is>
       </c>
     </row>
@@ -16695,7 +16698,7 @@
     <row r="14" ht="26" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
@@ -16803,7 +16806,7 @@
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B18" s="31" t="inlineStr">
@@ -16835,7 +16838,7 @@
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B19" s="31" t="inlineStr">
@@ -16894,10 +16897,8 @@
           <t>Net Bill Value (before taxes) [1+2-3]</t>
         </is>
       </c>
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>590.00</t>
-        </is>
+      <c r="B24" s="34" t="n">
+        <v>590</v>
       </c>
       <c r="C24" s="33" t="inlineStr">
         <is>
@@ -16911,10 +16912,8 @@
           <t>GST Collected</t>
         </is>
       </c>
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t>29.50</t>
-        </is>
+      <c r="B25" s="34" t="n">
+        <v>29.5</v>
       </c>
       <c r="C25" s="33" t="inlineStr">
         <is>
@@ -16928,10 +16927,8 @@
           <t>Total Customer Paid [4+5]</t>
         </is>
       </c>
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t>619.50</t>
-        </is>
+      <c r="B26" s="34" t="n">
+        <v>619.5</v>
       </c>
       <c r="C26" s="33" t="inlineStr">
         <is>
@@ -16945,10 +16942,8 @@
           <t>Commission charged on</t>
         </is>
       </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>495.60</t>
-        </is>
+      <c r="B27" s="34" t="n">
+        <v>495.6</v>
       </c>
       <c r="C27" s="33" t="inlineStr">
         <is>
@@ -16962,10 +16957,8 @@
           <t>GST Deduction</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>23.60</t>
-        </is>
+      <c r="B28" s="34" t="n">
+        <v>23.6</v>
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
@@ -16979,10 +16972,8 @@
           <t>Customer Cancellations / Complaint &amp; Cancellation Charges [18+19]</t>
         </is>
       </c>
-      <c r="B29" s="33" t="inlineStr">
-        <is>
-          <t>123.90</t>
-        </is>
+      <c r="B29" s="34" t="n">
+        <v>123.9</v>
       </c>
       <c r="C29" s="33" t="inlineStr">
         <is>
@@ -16996,10 +16987,8 @@
           <t>TDS</t>
         </is>
       </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
+      <c r="B30" s="34" t="n">
+        <v>0.47</v>
       </c>
       <c r="C30" s="33" t="inlineStr">
         <is>
@@ -17040,7 +17029,7 @@
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>₹590.00 × 20% — the value is not a supply because the restaurant was compensated at 80%</t>
+          <t>Value is not a supply because the restaurant was compensated at 80% of the order value</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17042,7 @@
       <c r="B35" s="17" t="n">
         <v>46118.33</v>
       </c>
-      <c r="C35" s="34" t="inlineStr">
+      <c r="C35" s="35" t="inlineStr">
         <is>
           <t>Value on which the 5% GST is discharged u/s 9(5)</t>
         </is>
@@ -17099,7 +17088,7 @@
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>₹118.00 × 5% — this GST is not payable and is deducted from the payout along with the value</t>
+          <t>This GST is not payable (the balance 20% is not a supply) and is deducted from the payout along with the value</t>
         </is>
       </c>
     </row>
@@ -17127,7 +17116,7 @@
       <c r="B40" s="17" t="n">
         <v>2305.92</v>
       </c>
-      <c r="C40" s="34" t="inlineStr">
+      <c r="C40" s="35" t="inlineStr">
         <is>
           <t>Ties the total GST billed to customers to the total GST discharged</t>
         </is>
@@ -17238,7 +17227,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -17279,7 +17268,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -17320,7 +17309,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -17361,7 +17350,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -17402,7 +17391,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -17443,7 +17432,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
@@ -17484,7 +17473,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -17525,7 +17514,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
@@ -17566,21 +17555,21 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
-        </is>
-      </c>
-      <c r="B13" s="35" t="inlineStr">
+          <t>27 – 30 Sep</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>No ads investment / adjustment this cycle</t>
         </is>
       </c>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="36" t="n"/>
-      <c r="E13" s="36" t="n"/>
-      <c r="F13" s="36" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="36" t="n"/>
-      <c r="I13" s="36" t="n"/>
+      <c r="C13" s="37" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="37" t="n"/>
+      <c r="G13" s="37" t="n"/>
+      <c r="H13" s="37" t="n"/>
+      <c r="I13" s="37" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -17647,11 +17636,11 @@
           <t>Nil — no adjustment or refund recovered by Swiggy in any of the five cycles</t>
         </is>
       </c>
-      <c r="C18" s="36" t="n"/>
-      <c r="D18" s="36" t="n"/>
-      <c r="E18" s="36" t="n"/>
-      <c r="F18" s="36" t="n"/>
-      <c r="G18" s="36" t="n"/>
+      <c r="C18" s="37" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="37" t="n"/>
+      <c r="G18" s="37" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
@@ -17750,7 +17739,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
@@ -17780,7 +17769,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -17810,7 +17799,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -17840,7 +17829,7 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
@@ -17870,7 +17859,7 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
@@ -17903,7 +17892,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E10" s="37" t="n">
+      <c r="E10" s="38" t="n">
         <v>75</v>
       </c>
     </row>
@@ -17998,7 +17987,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>01–05 Sep 2026</t>
+          <t>01 – 05 Sep</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
@@ -18023,7 +18012,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>06–12 Sep 2026</t>
+          <t>06 – 12 Sep</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
@@ -18048,7 +18037,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>13–19 Sep 2026</t>
+          <t>13 – 19 Sep</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
@@ -18073,7 +18062,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>20–26 Sep 2026</t>
+          <t>20 – 26 Sep</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
@@ -18098,7 +18087,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>27–30 Sep 2026</t>
+          <t>27 – 30 Sep</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
